--- a/outputs/report.xlsx
+++ b/outputs/report.xlsx
@@ -128,7 +128,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -168,6 +168,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0027AE60"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E67E22"/>
       </patternFill>
     </fill>
     <fill>
@@ -275,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -325,13 +330,13 @@
     <xf numFmtId="164" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -340,32 +345,35 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -383,43 +391,46 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -431,10 +442,10 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -525,7 +536,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Container Length Fill %</a:t>
+              <a:t>Container Volume Fill %</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -539,7 +550,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>Fill %</v>
+            <v>Vol Fill %</v>
           </tx>
           <spPr>
             <a:solidFill>
@@ -608,7 +619,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Fill %</a:t>
+                  <a:t>Vol Fill %</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -968,7 +979,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 01 Mar 2026  22:19   |   Objective: min_leftover</t>
+          <t>Generated: 02 Mar 2026  01:00   |   Objective: min_leftover</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1040,12 @@
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Avg container length fill</t>
+          <t>Avg container volume fill</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>88.4 %</t>
+          <t>72.8 %</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr"/>
@@ -1088,7 +1099,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Used (cm)</t>
+          <t>Len Used (cm)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1098,7 +1109,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Fill %</t>
+          <t>Vol Fill %</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -1133,7 +1144,7 @@
         <v>1203</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>99.8</v>
+        <v>96.7</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>42</v>
@@ -1159,7 +1170,7 @@
         <v>1203</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>99.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>40</v>
@@ -1185,7 +1196,7 @@
         <v>1203</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>99.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="E18" s="11" t="n">
         <v>40</v>
@@ -1211,7 +1222,7 @@
         <v>1203</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>99.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>40</v>
@@ -1237,7 +1248,7 @@
         <v>1203</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>99.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E20" s="11" t="n">
         <v>40</v>
@@ -1262,8 +1273,8 @@
       <c r="C21" s="15" t="n">
         <v>1203</v>
       </c>
-      <c r="D21" s="13" t="n">
-        <v>95</v>
+      <c r="D21" s="16" t="n">
+        <v>64.8</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>28</v>
@@ -1288,8 +1299,8 @@
       <c r="C22" s="12" t="n">
         <v>1203</v>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>95</v>
+      <c r="D22" s="17" t="n">
+        <v>51.6</v>
       </c>
       <c r="E22" s="11" t="n">
         <v>28</v>
@@ -1314,8 +1325,8 @@
       <c r="C23" s="15" t="n">
         <v>1203</v>
       </c>
-      <c r="D23" s="13" t="n">
-        <v>95</v>
+      <c r="D23" s="17" t="n">
+        <v>51.6</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>28</v>
@@ -1340,8 +1351,8 @@
       <c r="C24" s="12" t="n">
         <v>1203</v>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>13.2</v>
+      <c r="D24" s="17" t="n">
+        <v>7.4</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>4</v>
@@ -1396,14 +1407,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 1   —   Used 1201 / 1203 cm  (99.8%)   |   Pallets: 42   Weight: 0 kg   NP Boxes: 16</t>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 1   —   Vol Fill: 96.7%  |  Len used: 1201 / 1203 cm  (99.8%)   |   Pallets: 42   Weight: 0 kg   NP Boxes: 16</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -1447,7 +1458,7 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>115x77|89-130</t>
         </is>
@@ -1474,7 +1485,7 @@
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>115x77|89-130</t>
         </is>
@@ -1501,7 +1512,7 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1528,7 +1539,7 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1555,7 +1566,7 @@
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1582,7 +1593,7 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1609,7 +1620,7 @@
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1636,7 +1647,7 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1663,7 +1674,7 @@
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1690,7 +1701,7 @@
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1704,7 +1715,7 @@
         <v>115</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -1717,7 +1728,7 @@
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -1744,7 +1755,7 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  NP Box Zones</t>
         </is>
@@ -1788,12 +1799,12 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h17xd35cm | [8718861700350]</t>
         </is>
@@ -1815,12 +1826,12 @@
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]</t>
         </is>
@@ -1842,12 +1853,12 @@
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h32,5xd38cm | [8718861924237]</t>
         </is>
@@ -1869,12 +1880,12 @@
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h26xd30,5cm | [8720362378723]</t>
         </is>
@@ -1897,14 +1908,14 @@
     </row>
     <row r="21" ht="10" customHeight="1"/>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 2   —   Used 1195 / 1203 cm  (99.3%)   |   Pallets: 40   Weight: 0 kg   NP Boxes: 0</t>
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 2   —   Vol Fill: 96.6%  |  Len used: 1195 / 1203 cm  (99.3%)   |   Pallets: 40   Weight: 0 kg   NP Boxes: 0</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -1948,7 +1959,7 @@
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -1975,7 +1986,7 @@
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2002,7 +2013,7 @@
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2029,7 +2040,7 @@
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2056,7 +2067,7 @@
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2083,7 +2094,7 @@
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2110,7 +2121,7 @@
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2137,7 +2148,7 @@
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2164,7 +2175,7 @@
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2191,7 +2202,7 @@
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2219,14 +2230,14 @@
     </row>
     <row r="35" ht="10" customHeight="1"/>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 3   —   Used 1195 / 1203 cm  (99.3%)   |   Pallets: 40   Weight: 0 kg   NP Boxes: 0</t>
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 3   —   Vol Fill: 96.1%  |  Len used: 1195 / 1203 cm  (99.3%)   |   Pallets: 40   Weight: 0 kg   NP Boxes: 0</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -2270,7 +2281,7 @@
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2297,7 +2308,7 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2324,7 +2335,7 @@
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2351,7 +2362,7 @@
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2378,7 +2389,7 @@
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2405,7 +2416,7 @@
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2432,7 +2443,7 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2459,7 +2470,7 @@
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2486,7 +2497,7 @@
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2500,7 +2511,7 @@
         <v>115</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E47" s="11" t="n">
         <v>0</v>
@@ -2513,7 +2524,7 @@
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2541,14 +2552,14 @@
     </row>
     <row r="49" ht="10" customHeight="1"/>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 4   —   Used 1195 / 1203 cm  (99.3%)   |   Pallets: 40   Weight: 0 kg   NP Boxes: 0</t>
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 4   —   Vol Fill: 96.6%  |  Len used: 1195 / 1203 cm  (99.3%)   |   Pallets: 40   Weight: 0 kg   NP Boxes: 0</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -2592,7 +2603,7 @@
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2619,7 +2630,7 @@
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2646,7 +2657,7 @@
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2673,7 +2684,7 @@
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2687,7 +2698,7 @@
         <v>115</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E56" s="14" t="n">
         <v>0</v>
@@ -2700,7 +2711,7 @@
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2714,7 +2725,7 @@
         <v>115</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E57" s="11" t="n">
         <v>0</v>
@@ -2727,7 +2738,7 @@
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2741,7 +2752,7 @@
         <v>115</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E58" s="14" t="n">
         <v>0</v>
@@ -2754,7 +2765,7 @@
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2768,7 +2779,7 @@
         <v>115</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E59" s="11" t="n">
         <v>0</v>
@@ -2781,7 +2792,7 @@
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="A60" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2795,7 +2806,7 @@
         <v>115</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E60" s="14" t="n">
         <v>0</v>
@@ -2808,7 +2819,7 @@
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2822,7 +2833,7 @@
         <v>115</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E61" s="11" t="n">
         <v>0</v>
@@ -2835,7 +2846,7 @@
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2863,14 +2874,14 @@
     </row>
     <row r="63" ht="10" customHeight="1"/>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 5   —   Used 1195 / 1203 cm  (99.3%)   |   Pallets: 40   Weight: 0 kg   NP Boxes: 0</t>
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 5   —   Vol Fill: 93.4%  |  Len used: 1195 / 1203 cm  (99.3%)   |   Pallets: 40   Weight: 0 kg   NP Boxes: 0</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -2914,7 +2925,7 @@
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="20" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2941,7 +2952,7 @@
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="20" t="inlineStr">
+      <c r="A68" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2968,7 +2979,7 @@
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="20" t="inlineStr">
+      <c r="A69" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -2995,7 +3006,7 @@
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="20" t="inlineStr">
+      <c r="A70" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -3009,7 +3020,7 @@
         <v>115</v>
       </c>
       <c r="D70" s="14" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E70" s="14" t="n">
         <v>0</v>
@@ -3022,7 +3033,7 @@
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -3036,7 +3047,7 @@
         <v>115</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E71" s="11" t="n">
         <v>0</v>
@@ -3049,7 +3060,7 @@
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
+      <c r="A72" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -3063,7 +3074,7 @@
         <v>115</v>
       </c>
       <c r="D72" s="14" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E72" s="14" t="n">
         <v>0</v>
@@ -3076,7 +3087,7 @@
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
+      <c r="A73" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -3090,7 +3101,7 @@
         <v>115</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E73" s="11" t="n">
         <v>0</v>
@@ -3103,7 +3114,7 @@
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="20" t="inlineStr">
+      <c r="A74" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -3130,7 +3141,7 @@
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="20" t="inlineStr">
+      <c r="A75" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -3157,7 +3168,7 @@
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="20" t="inlineStr">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t>115x115|89-130</t>
         </is>
@@ -3185,14 +3196,14 @@
     </row>
     <row r="77" ht="10" customHeight="1"/>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 6   —   Used 1143 / 1203 cm  (95.0%)   |   Pallets: 28   Weight: 0 kg   NP Boxes: 69</t>
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 6   —   Vol Fill: 64.8%  |  Len used: 1143 / 1203 cm  (95.0%)   |   Pallets: 28   Weight: 0 kg   NP Boxes: 69</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="18" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -3236,7 +3247,7 @@
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="19" t="inlineStr">
+      <c r="A81" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3263,7 +3274,7 @@
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="19" t="inlineStr">
+      <c r="A82" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3290,7 +3301,7 @@
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="19" t="inlineStr">
+      <c r="A83" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3317,7 +3328,7 @@
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="19" t="inlineStr">
+      <c r="A84" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3344,7 +3355,7 @@
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="19" t="inlineStr">
+      <c r="A85" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3371,7 +3382,7 @@
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="19" t="inlineStr">
+      <c r="A86" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3398,7 +3409,7 @@
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="19" t="inlineStr">
+      <c r="A87" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3425,7 +3436,7 @@
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="19" t="inlineStr">
+      <c r="A88" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3452,7 +3463,7 @@
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="19" t="inlineStr">
+      <c r="A89" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3479,7 +3490,7 @@
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
+      <c r="A90" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3506,7 +3517,7 @@
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="19" t="inlineStr">
+      <c r="A91" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3533,7 +3544,7 @@
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="19" t="inlineStr">
+      <c r="A92" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3560,7 +3571,7 @@
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="19" t="inlineStr">
+      <c r="A93" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3587,7 +3598,7 @@
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="19" t="inlineStr">
+      <c r="A94" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -3614,7 +3625,7 @@
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="18" t="inlineStr">
+      <c r="A95" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  NP Box Zones</t>
         </is>
@@ -3658,12 +3669,12 @@
       </c>
     </row>
     <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="21" t="inlineStr">
+      <c r="A97" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B97" s="21" t="inlineStr">
+      <c r="B97" s="22" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]</t>
         </is>
@@ -3685,12 +3696,12 @@
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="21" t="inlineStr">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B98" s="21" t="inlineStr">
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h32,5xd38cm | [8718861924237]</t>
         </is>
@@ -3712,12 +3723,12 @@
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="21" t="inlineStr">
+      <c r="A99" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B99" s="21" t="inlineStr">
+      <c r="B99" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h26xd30,5cm | [8720362378723]</t>
         </is>
@@ -3739,12 +3750,12 @@
       </c>
     </row>
     <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="21" t="inlineStr">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B100" s="21" t="inlineStr">
+      <c r="B100" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h40xd45cm | [8720362378730]</t>
         </is>
@@ -3766,12 +3777,12 @@
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="21" t="inlineStr">
+      <c r="A101" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B101" s="21" t="inlineStr">
+      <c r="B101" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h40xd45cm | [8720362378730]</t>
         </is>
@@ -3793,12 +3804,12 @@
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="21" t="inlineStr">
+      <c r="A102" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B102" s="21" t="inlineStr">
+      <c r="B102" s="22" t="inlineStr">
         <is>
           <t>Rio pot round cream - h33,5xd37cm | [8720362676607]</t>
         </is>
@@ -3820,12 +3831,12 @@
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="21" t="inlineStr">
+      <c r="A103" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B103" s="21" t="inlineStr">
+      <c r="B103" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round d. grey beehive - h26xd30,5cm | [8720967833894]</t>
         </is>
@@ -3847,12 +3858,12 @@
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="21" t="inlineStr">
+      <c r="A104" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B104" s="21" t="inlineStr">
+      <c r="B104" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round d. grey beehive - h26xd30,5cm | [8720967833894]</t>
         </is>
@@ -3874,12 +3885,12 @@
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+      <c r="A105" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B105" s="21" t="inlineStr">
+      <c r="B105" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. brown beehive glaze - h26xd30,5cm | [8720967833931]</t>
         </is>
@@ -3901,12 +3912,12 @@
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="21" t="inlineStr">
+      <c r="A106" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B106" s="21" t="inlineStr">
+      <c r="B106" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. brown beehive glaze - h32,5xd38cm | [8720967833948]</t>
         </is>
@@ -3928,12 +3939,12 @@
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="21" t="inlineStr">
+      <c r="A107" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B107" s="21" t="inlineStr">
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. brown beehive glaze - h32,5xd38cm | [8720967833948]</t>
         </is>
@@ -3955,12 +3966,12 @@
       </c>
     </row>
     <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="21" t="inlineStr">
+      <c r="A108" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B108" s="21" t="inlineStr">
+      <c r="B108" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. brown beehive glaze - h40xd45cm | [8720967833955]</t>
         </is>
@@ -3982,12 +3993,12 @@
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="21" t="inlineStr">
+      <c r="A109" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B109" s="21" t="inlineStr">
+      <c r="B109" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round blue beehive glaze - h40xd45cm | [8720967834013]</t>
         </is>
@@ -4009,12 +4020,12 @@
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="21" t="inlineStr">
+      <c r="A110" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B110" s="21" t="inlineStr">
+      <c r="B110" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round l. brown beehive glaze - h40xd45cm | [8720967833955]</t>
         </is>
@@ -4036,12 +4047,12 @@
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="21" t="inlineStr">
+      <c r="A111" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B111" s="21" t="inlineStr">
+      <c r="B111" s="22" t="inlineStr">
         <is>
           <t>Bravo pot round blue beehive glaze - h40xd45cm | [8720967834013]</t>
         </is>
@@ -4063,12 +4074,12 @@
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="21" t="inlineStr">
+      <c r="A112" s="22" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B112" s="21" t="inlineStr">
+      <c r="B112" s="22" t="inlineStr">
         <is>
           <t>Rio pot round green - h40,5xd45cm | [8720967834082]</t>
         </is>
@@ -4091,14 +4102,14 @@
     </row>
     <row r="113" ht="10" customHeight="1"/>
     <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 7   —   Used 1143 / 1203 cm  (95.0%)   |   Pallets: 28   Weight: 0 kg   NP Boxes: 0</t>
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 7   —   Vol Fill: 51.6%  |  Len used: 1143 / 1203 cm  (95.0%)   |   Pallets: 28   Weight: 0 kg   NP Boxes: 0</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="18" t="inlineStr">
+      <c r="A115" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -4142,7 +4153,7 @@
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="19" t="inlineStr">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4169,7 +4180,7 @@
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="19" t="inlineStr">
+      <c r="A118" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4196,7 +4207,7 @@
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="19" t="inlineStr">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4223,7 +4234,7 @@
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="19" t="inlineStr">
+      <c r="A120" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4250,7 +4261,7 @@
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="19" t="inlineStr">
+      <c r="A121" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4277,7 +4288,7 @@
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="19" t="inlineStr">
+      <c r="A122" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4304,7 +4315,7 @@
       </c>
     </row>
     <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="19" t="inlineStr">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4331,7 +4342,7 @@
       </c>
     </row>
     <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="19" t="inlineStr">
+      <c r="A124" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4358,7 +4369,7 @@
       </c>
     </row>
     <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="19" t="inlineStr">
+      <c r="A125" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4385,7 +4396,7 @@
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="19" t="inlineStr">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4412,7 +4423,7 @@
       </c>
     </row>
     <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="19" t="inlineStr">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4439,7 +4450,7 @@
       </c>
     </row>
     <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="19" t="inlineStr">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4466,7 +4477,7 @@
       </c>
     </row>
     <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="19" t="inlineStr">
+      <c r="A129" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4493,7 +4504,7 @@
       </c>
     </row>
     <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="19" t="inlineStr">
+      <c r="A130" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4521,14 +4532,14 @@
     </row>
     <row r="131" ht="10" customHeight="1"/>
     <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 8   —   Used 1143 / 1203 cm  (95.0%)   |   Pallets: 28   Weight: 0 kg   NP Boxes: 0</t>
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 8   —   Vol Fill: 51.6%  |  Len used: 1143 / 1203 cm  (95.0%)   |   Pallets: 28   Weight: 0 kg   NP Boxes: 0</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="18" t="inlineStr">
+      <c r="A133" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -4572,7 +4583,7 @@
       </c>
     </row>
     <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="19" t="inlineStr">
+      <c r="A135" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4599,7 +4610,7 @@
       </c>
     </row>
     <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="19" t="inlineStr">
+      <c r="A136" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4626,7 +4637,7 @@
       </c>
     </row>
     <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="19" t="inlineStr">
+      <c r="A137" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4653,7 +4664,7 @@
       </c>
     </row>
     <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="19" t="inlineStr">
+      <c r="A138" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4680,7 +4691,7 @@
       </c>
     </row>
     <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="19" t="inlineStr">
+      <c r="A139" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4707,7 +4718,7 @@
       </c>
     </row>
     <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="19" t="inlineStr">
+      <c r="A140" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4734,7 +4745,7 @@
       </c>
     </row>
     <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="19" t="inlineStr">
+      <c r="A141" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4761,7 +4772,7 @@
       </c>
     </row>
     <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="19" t="inlineStr">
+      <c r="A142" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4788,7 +4799,7 @@
       </c>
     </row>
     <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="19" t="inlineStr">
+      <c r="A143" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4815,7 +4826,7 @@
       </c>
     </row>
     <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="19" t="inlineStr">
+      <c r="A144" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4842,7 +4853,7 @@
       </c>
     </row>
     <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="19" t="inlineStr">
+      <c r="A145" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4869,7 +4880,7 @@
       </c>
     </row>
     <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="19" t="inlineStr">
+      <c r="A146" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4896,7 +4907,7 @@
       </c>
     </row>
     <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="19" t="inlineStr">
+      <c r="A147" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4923,7 +4934,7 @@
       </c>
     </row>
     <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="19" t="inlineStr">
+      <c r="A148" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -4951,14 +4962,14 @@
     </row>
     <row r="149" ht="10" customHeight="1"/>
     <row r="150" ht="24" customHeight="1">
-      <c r="A150" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTAINER 9   —   Used 159 / 1203 cm  (13.2%)   |   Pallets: 4   Weight: 0 kg   NP Boxes: 0</t>
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTAINER 9   —   Vol Fill: 7.4%  |  Len used: 159 / 1203 cm  (13.2%)   |   Pallets: 4   Weight: 0 kg   NP Boxes: 0</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="18" t="inlineStr">
+      <c r="A151" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pallet Row Blocks</t>
         </is>
@@ -5002,7 +5013,7 @@
       </c>
     </row>
     <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="19" t="inlineStr">
+      <c r="A153" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -5029,7 +5040,7 @@
       </c>
     </row>
     <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="19" t="inlineStr">
+      <c r="A154" s="20" t="inlineStr">
         <is>
           <t>115x77|&gt;130</t>
         </is>
@@ -5201,7 +5212,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PACKING LAYOUT   (each cell ≈ 12 cm • colours show block type  •  green = recommended additions)</t>
         </is>
@@ -5209,2511 +5220,2511 @@
     </row>
     <row r="2" ht="5" customHeight="1"/>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  115×115 pallet</t>
         </is>
       </c>
-      <c r="B3" s="24" t="n"/>
-      <c r="D3" s="25" t="inlineStr">
+      <c r="B3" s="25" t="n"/>
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  115×108 pallet</t>
         </is>
       </c>
-      <c r="E3" s="24" t="n"/>
-      <c r="G3" s="26" t="inlineStr">
+      <c r="E3" s="25" t="n"/>
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  115×77  pallet</t>
         </is>
       </c>
-      <c r="H3" s="24" t="n"/>
-      <c r="J3" s="27" t="inlineStr">
+      <c r="H3" s="25" t="n"/>
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  77×77   pallet</t>
         </is>
       </c>
-      <c r="K3" s="24" t="n"/>
-      <c r="M3" s="28" t="inlineStr">
+      <c r="K3" s="25" t="n"/>
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NP box zone</t>
         </is>
       </c>
-      <c r="N3" s="24" t="n"/>
-      <c r="P3" s="29" t="inlineStr">
+      <c r="N3" s="25" t="n"/>
+      <c r="P3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Empty space</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="n"/>
-      <c r="S3" s="30" t="inlineStr">
+      <c r="Q3" s="25" t="n"/>
+      <c r="S3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rec. pallets</t>
         </is>
       </c>
-      <c r="T3" s="24" t="n"/>
-      <c r="V3" s="31" t="inlineStr">
+      <c r="T3" s="25" t="n"/>
+      <c r="V3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rec. NP boxes</t>
         </is>
       </c>
-      <c r="W3" s="24" t="n"/>
+      <c r="W3" s="25" t="n"/>
     </row>
     <row r="4" ht="5" customHeight="1"/>
     <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Fill %</t>
-        </is>
-      </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>Vol Fill %</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="33" t="inlineStr">
+      <c r="L5" s="34" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T5" s="33" t="inlineStr">
+      <c r="T5" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AC5" s="33" t="inlineStr">
+      <c r="AC5" s="34" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AK5" s="33" t="inlineStr">
+      <c r="AK5" s="34" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="AS5" s="33" t="inlineStr">
+      <c r="AS5" s="34" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="BB5" s="33" t="inlineStr">
+      <c r="BB5" s="34" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="BJ5" s="33" t="inlineStr">
+      <c r="BJ5" s="34" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="BR5" s="33" t="inlineStr">
+      <c r="BR5" s="34" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="CA5" s="33" t="inlineStr">
+      <c r="CA5" s="34" t="inlineStr">
         <is>
           <t>900</t>
         </is>
       </c>
-      <c r="CI5" s="33" t="inlineStr">
+      <c r="CI5" s="34" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="CQ5" s="33" t="inlineStr">
+      <c r="CQ5" s="34" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="CZ5" s="33" t="inlineStr">
+      <c r="CZ5" s="34" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Cont. 1</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>99.8%</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>96.7%</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>115x77(4p)</t>
         </is>
       </c>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
-      <c r="H6" s="38" t="n"/>
-      <c r="I6" s="38" t="n"/>
-      <c r="J6" s="37" t="inlineStr">
+      <c r="E6" s="39" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="39" t="n"/>
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="39" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
         <is>
           <t>115x77(4p)</t>
         </is>
       </c>
-      <c r="K6" s="38" t="n"/>
-      <c r="L6" s="38" t="n"/>
-      <c r="M6" s="38" t="n"/>
-      <c r="N6" s="38" t="n"/>
-      <c r="O6" s="38" t="n"/>
-      <c r="P6" s="38" t="n"/>
-      <c r="Q6" s="39" t="inlineStr">
+      <c r="K6" s="39" t="n"/>
+      <c r="L6" s="39" t="n"/>
+      <c r="M6" s="39" t="n"/>
+      <c r="N6" s="39" t="n"/>
+      <c r="O6" s="39" t="n"/>
+      <c r="P6" s="39" t="n"/>
+      <c r="Q6" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="R6" s="40" t="n"/>
-      <c r="S6" s="40" t="n"/>
-      <c r="T6" s="40" t="n"/>
-      <c r="U6" s="40" t="n"/>
-      <c r="V6" s="40" t="n"/>
-      <c r="W6" s="40" t="n"/>
-      <c r="X6" s="40" t="n"/>
-      <c r="Y6" s="40" t="n"/>
-      <c r="Z6" s="40" t="n"/>
-      <c r="AA6" s="39" t="inlineStr">
+      <c r="R6" s="41" t="n"/>
+      <c r="S6" s="41" t="n"/>
+      <c r="T6" s="41" t="n"/>
+      <c r="U6" s="41" t="n"/>
+      <c r="V6" s="41" t="n"/>
+      <c r="W6" s="41" t="n"/>
+      <c r="X6" s="41" t="n"/>
+      <c r="Y6" s="41" t="n"/>
+      <c r="Z6" s="41" t="n"/>
+      <c r="AA6" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AB6" s="40" t="n"/>
-      <c r="AC6" s="40" t="n"/>
-      <c r="AD6" s="40" t="n"/>
-      <c r="AE6" s="40" t="n"/>
-      <c r="AF6" s="40" t="n"/>
-      <c r="AG6" s="40" t="n"/>
-      <c r="AH6" s="40" t="n"/>
-      <c r="AI6" s="40" t="n"/>
-      <c r="AJ6" s="40" t="n"/>
-      <c r="AK6" s="39" t="inlineStr">
+      <c r="AB6" s="41" t="n"/>
+      <c r="AC6" s="41" t="n"/>
+      <c r="AD6" s="41" t="n"/>
+      <c r="AE6" s="41" t="n"/>
+      <c r="AF6" s="41" t="n"/>
+      <c r="AG6" s="41" t="n"/>
+      <c r="AH6" s="41" t="n"/>
+      <c r="AI6" s="41" t="n"/>
+      <c r="AJ6" s="41" t="n"/>
+      <c r="AK6" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AL6" s="40" t="n"/>
-      <c r="AM6" s="40" t="n"/>
-      <c r="AN6" s="40" t="n"/>
-      <c r="AO6" s="40" t="n"/>
-      <c r="AP6" s="40" t="n"/>
-      <c r="AQ6" s="40" t="n"/>
-      <c r="AR6" s="40" t="n"/>
-      <c r="AS6" s="40" t="n"/>
-      <c r="AT6" s="40" t="n"/>
-      <c r="AU6" s="39" t="inlineStr">
+      <c r="AL6" s="41" t="n"/>
+      <c r="AM6" s="41" t="n"/>
+      <c r="AN6" s="41" t="n"/>
+      <c r="AO6" s="41" t="n"/>
+      <c r="AP6" s="41" t="n"/>
+      <c r="AQ6" s="41" t="n"/>
+      <c r="AR6" s="41" t="n"/>
+      <c r="AS6" s="41" t="n"/>
+      <c r="AT6" s="41" t="n"/>
+      <c r="AU6" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AV6" s="40" t="n"/>
-      <c r="AW6" s="40" t="n"/>
-      <c r="AX6" s="40" t="n"/>
-      <c r="AY6" s="40" t="n"/>
-      <c r="AZ6" s="40" t="n"/>
-      <c r="BA6" s="40" t="n"/>
-      <c r="BB6" s="40" t="n"/>
-      <c r="BC6" s="40" t="n"/>
-      <c r="BD6" s="40" t="n"/>
-      <c r="BE6" s="39" t="inlineStr">
+      <c r="AV6" s="41" t="n"/>
+      <c r="AW6" s="41" t="n"/>
+      <c r="AX6" s="41" t="n"/>
+      <c r="AY6" s="41" t="n"/>
+      <c r="AZ6" s="41" t="n"/>
+      <c r="BA6" s="41" t="n"/>
+      <c r="BB6" s="41" t="n"/>
+      <c r="BC6" s="41" t="n"/>
+      <c r="BD6" s="41" t="n"/>
+      <c r="BE6" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BF6" s="40" t="n"/>
-      <c r="BG6" s="40" t="n"/>
-      <c r="BH6" s="40" t="n"/>
-      <c r="BI6" s="40" t="n"/>
-      <c r="BJ6" s="40" t="n"/>
-      <c r="BK6" s="40" t="n"/>
-      <c r="BL6" s="40" t="n"/>
-      <c r="BM6" s="40" t="n"/>
-      <c r="BN6" s="40" t="n"/>
-      <c r="BO6" s="39" t="inlineStr">
+      <c r="BF6" s="41" t="n"/>
+      <c r="BG6" s="41" t="n"/>
+      <c r="BH6" s="41" t="n"/>
+      <c r="BI6" s="41" t="n"/>
+      <c r="BJ6" s="41" t="n"/>
+      <c r="BK6" s="41" t="n"/>
+      <c r="BL6" s="41" t="n"/>
+      <c r="BM6" s="41" t="n"/>
+      <c r="BN6" s="41" t="n"/>
+      <c r="BO6" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BP6" s="40" t="n"/>
-      <c r="BQ6" s="40" t="n"/>
-      <c r="BR6" s="40" t="n"/>
-      <c r="BS6" s="40" t="n"/>
-      <c r="BT6" s="40" t="n"/>
-      <c r="BU6" s="40" t="n"/>
-      <c r="BV6" s="40" t="n"/>
-      <c r="BW6" s="40" t="n"/>
-      <c r="BX6" s="40" t="n"/>
-      <c r="BY6" s="39" t="inlineStr">
+      <c r="BP6" s="41" t="n"/>
+      <c r="BQ6" s="41" t="n"/>
+      <c r="BR6" s="41" t="n"/>
+      <c r="BS6" s="41" t="n"/>
+      <c r="BT6" s="41" t="n"/>
+      <c r="BU6" s="41" t="n"/>
+      <c r="BV6" s="41" t="n"/>
+      <c r="BW6" s="41" t="n"/>
+      <c r="BX6" s="41" t="n"/>
+      <c r="BY6" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BZ6" s="40" t="n"/>
-      <c r="CA6" s="40" t="n"/>
-      <c r="CB6" s="40" t="n"/>
-      <c r="CC6" s="40" t="n"/>
-      <c r="CD6" s="40" t="n"/>
-      <c r="CE6" s="40" t="n"/>
-      <c r="CF6" s="40" t="n"/>
-      <c r="CG6" s="40" t="n"/>
-      <c r="CH6" s="40" t="n"/>
-      <c r="CI6" s="39" t="inlineStr">
+      <c r="BZ6" s="41" t="n"/>
+      <c r="CA6" s="41" t="n"/>
+      <c r="CB6" s="41" t="n"/>
+      <c r="CC6" s="41" t="n"/>
+      <c r="CD6" s="41" t="n"/>
+      <c r="CE6" s="41" t="n"/>
+      <c r="CF6" s="41" t="n"/>
+      <c r="CG6" s="41" t="n"/>
+      <c r="CH6" s="41" t="n"/>
+      <c r="CI6" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CJ6" s="40" t="n"/>
-      <c r="CK6" s="40" t="n"/>
-      <c r="CL6" s="40" t="n"/>
-      <c r="CM6" s="40" t="n"/>
-      <c r="CN6" s="40" t="n"/>
-      <c r="CO6" s="40" t="n"/>
-      <c r="CP6" s="40" t="n"/>
-      <c r="CQ6" s="40" t="n"/>
-      <c r="CR6" s="40" t="n"/>
-      <c r="CS6" s="37" t="inlineStr">
+      <c r="CJ6" s="41" t="n"/>
+      <c r="CK6" s="41" t="n"/>
+      <c r="CL6" s="41" t="n"/>
+      <c r="CM6" s="41" t="n"/>
+      <c r="CN6" s="41" t="n"/>
+      <c r="CO6" s="41" t="n"/>
+      <c r="CP6" s="41" t="n"/>
+      <c r="CQ6" s="41" t="n"/>
+      <c r="CR6" s="41" t="n"/>
+      <c r="CS6" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CT6" s="38" t="n"/>
-      <c r="CU6" s="38" t="n"/>
-      <c r="CV6" s="38" t="n"/>
-      <c r="CW6" s="38" t="n"/>
-      <c r="CX6" s="38" t="n"/>
-      <c r="CY6" s="38" t="n"/>
-      <c r="CZ6" s="38" t="n"/>
+      <c r="CT6" s="39" t="n"/>
+      <c r="CU6" s="39" t="n"/>
+      <c r="CV6" s="39" t="n"/>
+      <c r="CW6" s="39" t="n"/>
+      <c r="CX6" s="39" t="n"/>
+      <c r="CY6" s="39" t="n"/>
+      <c r="CZ6" s="39" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>NP Boxes</t>
         </is>
       </c>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
-      <c r="I7" s="41" t="n"/>
-      <c r="J7" s="41" t="n"/>
-      <c r="K7" s="41" t="n"/>
-      <c r="L7" s="41" t="n"/>
-      <c r="M7" s="41" t="n"/>
-      <c r="N7" s="41" t="n"/>
-      <c r="O7" s="41" t="n"/>
-      <c r="P7" s="41" t="n"/>
-      <c r="Q7" s="41" t="n"/>
-      <c r="R7" s="41" t="n"/>
-      <c r="S7" s="41" t="n"/>
-      <c r="T7" s="41" t="n"/>
-      <c r="U7" s="41" t="n"/>
-      <c r="V7" s="41" t="n"/>
-      <c r="W7" s="41" t="n"/>
-      <c r="X7" s="41" t="n"/>
-      <c r="Y7" s="41" t="n"/>
-      <c r="Z7" s="41" t="n"/>
-      <c r="AA7" s="41" t="n"/>
-      <c r="AB7" s="41" t="n"/>
-      <c r="AC7" s="41" t="n"/>
-      <c r="AD7" s="41" t="n"/>
-      <c r="AE7" s="41" t="n"/>
-      <c r="AF7" s="41" t="n"/>
-      <c r="AG7" s="41" t="n"/>
-      <c r="AH7" s="41" t="n"/>
-      <c r="AI7" s="41" t="n"/>
-      <c r="AJ7" s="41" t="n"/>
-      <c r="AK7" s="41" t="n"/>
-      <c r="AL7" s="41" t="n"/>
-      <c r="AM7" s="41" t="n"/>
-      <c r="AN7" s="41" t="n"/>
-      <c r="AO7" s="41" t="n"/>
-      <c r="AP7" s="41" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
-      <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="41" t="n"/>
-      <c r="AT7" s="41" t="n"/>
-      <c r="AU7" s="41" t="n"/>
-      <c r="AV7" s="41" t="n"/>
-      <c r="AW7" s="41" t="n"/>
-      <c r="AX7" s="41" t="n"/>
-      <c r="AY7" s="41" t="n"/>
-      <c r="AZ7" s="41" t="n"/>
-      <c r="BA7" s="41" t="n"/>
-      <c r="BB7" s="41" t="n"/>
-      <c r="BC7" s="41" t="n"/>
-      <c r="BD7" s="41" t="n"/>
-      <c r="BE7" s="41" t="n"/>
-      <c r="BF7" s="41" t="n"/>
-      <c r="BG7" s="41" t="n"/>
-      <c r="BH7" s="41" t="n"/>
-      <c r="BI7" s="41" t="n"/>
-      <c r="BJ7" s="41" t="n"/>
-      <c r="BK7" s="41" t="n"/>
-      <c r="BL7" s="41" t="n"/>
-      <c r="BM7" s="41" t="n"/>
-      <c r="BN7" s="41" t="n"/>
-      <c r="BO7" s="41" t="n"/>
-      <c r="BP7" s="41" t="n"/>
-      <c r="BQ7" s="41" t="n"/>
-      <c r="BR7" s="41" t="n"/>
-      <c r="BS7" s="41" t="n"/>
-      <c r="BT7" s="41" t="n"/>
-      <c r="BU7" s="41" t="n"/>
-      <c r="BV7" s="41" t="n"/>
-      <c r="BW7" s="41" t="n"/>
-      <c r="BX7" s="41" t="n"/>
-      <c r="BY7" s="41" t="n"/>
-      <c r="BZ7" s="41" t="n"/>
-      <c r="CA7" s="41" t="n"/>
-      <c r="CB7" s="41" t="n"/>
-      <c r="CC7" s="41" t="n"/>
-      <c r="CD7" s="41" t="n"/>
-      <c r="CE7" s="41" t="n"/>
-      <c r="CF7" s="41" t="n"/>
-      <c r="CG7" s="41" t="n"/>
-      <c r="CH7" s="41" t="n"/>
-      <c r="CI7" s="41" t="n"/>
-      <c r="CJ7" s="41" t="n"/>
-      <c r="CK7" s="41" t="n"/>
-      <c r="CL7" s="41" t="n"/>
-      <c r="CM7" s="41" t="n"/>
-      <c r="CN7" s="41" t="n"/>
-      <c r="CO7" s="41" t="n"/>
-      <c r="CP7" s="41" t="n"/>
-      <c r="CQ7" s="41" t="n"/>
-      <c r="CR7" s="41" t="n"/>
-      <c r="CS7" s="42" t="inlineStr">
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="42" t="n"/>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="42" t="n"/>
+      <c r="H7" s="42" t="n"/>
+      <c r="I7" s="42" t="n"/>
+      <c r="J7" s="42" t="n"/>
+      <c r="K7" s="42" t="n"/>
+      <c r="L7" s="42" t="n"/>
+      <c r="M7" s="42" t="n"/>
+      <c r="N7" s="42" t="n"/>
+      <c r="O7" s="42" t="n"/>
+      <c r="P7" s="42" t="n"/>
+      <c r="Q7" s="42" t="n"/>
+      <c r="R7" s="42" t="n"/>
+      <c r="S7" s="42" t="n"/>
+      <c r="T7" s="42" t="n"/>
+      <c r="U7" s="42" t="n"/>
+      <c r="V7" s="42" t="n"/>
+      <c r="W7" s="42" t="n"/>
+      <c r="X7" s="42" t="n"/>
+      <c r="Y7" s="42" t="n"/>
+      <c r="Z7" s="42" t="n"/>
+      <c r="AA7" s="42" t="n"/>
+      <c r="AB7" s="42" t="n"/>
+      <c r="AC7" s="42" t="n"/>
+      <c r="AD7" s="42" t="n"/>
+      <c r="AE7" s="42" t="n"/>
+      <c r="AF7" s="42" t="n"/>
+      <c r="AG7" s="42" t="n"/>
+      <c r="AH7" s="42" t="n"/>
+      <c r="AI7" s="42" t="n"/>
+      <c r="AJ7" s="42" t="n"/>
+      <c r="AK7" s="42" t="n"/>
+      <c r="AL7" s="42" t="n"/>
+      <c r="AM7" s="42" t="n"/>
+      <c r="AN7" s="42" t="n"/>
+      <c r="AO7" s="42" t="n"/>
+      <c r="AP7" s="42" t="n"/>
+      <c r="AQ7" s="42" t="n"/>
+      <c r="AR7" s="42" t="n"/>
+      <c r="AS7" s="42" t="n"/>
+      <c r="AT7" s="42" t="n"/>
+      <c r="AU7" s="42" t="n"/>
+      <c r="AV7" s="42" t="n"/>
+      <c r="AW7" s="42" t="n"/>
+      <c r="AX7" s="42" t="n"/>
+      <c r="AY7" s="42" t="n"/>
+      <c r="AZ7" s="42" t="n"/>
+      <c r="BA7" s="42" t="n"/>
+      <c r="BB7" s="42" t="n"/>
+      <c r="BC7" s="42" t="n"/>
+      <c r="BD7" s="42" t="n"/>
+      <c r="BE7" s="42" t="n"/>
+      <c r="BF7" s="42" t="n"/>
+      <c r="BG7" s="42" t="n"/>
+      <c r="BH7" s="42" t="n"/>
+      <c r="BI7" s="42" t="n"/>
+      <c r="BJ7" s="42" t="n"/>
+      <c r="BK7" s="42" t="n"/>
+      <c r="BL7" s="42" t="n"/>
+      <c r="BM7" s="42" t="n"/>
+      <c r="BN7" s="42" t="n"/>
+      <c r="BO7" s="42" t="n"/>
+      <c r="BP7" s="42" t="n"/>
+      <c r="BQ7" s="42" t="n"/>
+      <c r="BR7" s="42" t="n"/>
+      <c r="BS7" s="42" t="n"/>
+      <c r="BT7" s="42" t="n"/>
+      <c r="BU7" s="42" t="n"/>
+      <c r="BV7" s="42" t="n"/>
+      <c r="BW7" s="42" t="n"/>
+      <c r="BX7" s="42" t="n"/>
+      <c r="BY7" s="42" t="n"/>
+      <c r="BZ7" s="42" t="n"/>
+      <c r="CA7" s="42" t="n"/>
+      <c r="CB7" s="42" t="n"/>
+      <c r="CC7" s="42" t="n"/>
+      <c r="CD7" s="42" t="n"/>
+      <c r="CE7" s="42" t="n"/>
+      <c r="CF7" s="42" t="n"/>
+      <c r="CG7" s="42" t="n"/>
+      <c r="CH7" s="42" t="n"/>
+      <c r="CI7" s="42" t="n"/>
+      <c r="CJ7" s="42" t="n"/>
+      <c r="CK7" s="42" t="n"/>
+      <c r="CL7" s="42" t="n"/>
+      <c r="CM7" s="42" t="n"/>
+      <c r="CN7" s="42" t="n"/>
+      <c r="CO7" s="42" t="n"/>
+      <c r="CP7" s="42" t="n"/>
+      <c r="CQ7" s="42" t="n"/>
+      <c r="CR7" s="42" t="n"/>
+      <c r="CS7" s="43" t="inlineStr">
         <is>
           <t>16b</t>
         </is>
       </c>
-      <c r="CT7" s="43" t="n"/>
-      <c r="CU7" s="43" t="n"/>
-      <c r="CV7" s="43" t="n"/>
-      <c r="CW7" s="43" t="n"/>
-      <c r="CX7" s="43" t="n"/>
-      <c r="CY7" s="43" t="n"/>
-      <c r="CZ7" s="43" t="n"/>
+      <c r="CT7" s="44" t="n"/>
+      <c r="CU7" s="44" t="n"/>
+      <c r="CV7" s="44" t="n"/>
+      <c r="CW7" s="44" t="n"/>
+      <c r="CX7" s="44" t="n"/>
+      <c r="CY7" s="44" t="n"/>
+      <c r="CZ7" s="44" t="n"/>
     </row>
     <row r="8" ht="4" customHeight="1"/>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Cont. 2</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>99.3%</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>96.6%</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D9" s="39" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="E9" s="40" t="n"/>
-      <c r="F9" s="40" t="n"/>
-      <c r="G9" s="40" t="n"/>
-      <c r="H9" s="40" t="n"/>
-      <c r="I9" s="40" t="n"/>
-      <c r="J9" s="40" t="n"/>
-      <c r="K9" s="40" t="n"/>
-      <c r="L9" s="40" t="n"/>
-      <c r="M9" s="40" t="n"/>
-      <c r="N9" s="39" t="inlineStr">
+      <c r="E9" s="41" t="n"/>
+      <c r="F9" s="41" t="n"/>
+      <c r="G9" s="41" t="n"/>
+      <c r="H9" s="41" t="n"/>
+      <c r="I9" s="41" t="n"/>
+      <c r="J9" s="41" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="41" t="n"/>
+      <c r="M9" s="41" t="n"/>
+      <c r="N9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="O9" s="40" t="n"/>
-      <c r="P9" s="40" t="n"/>
-      <c r="Q9" s="40" t="n"/>
-      <c r="R9" s="40" t="n"/>
-      <c r="S9" s="40" t="n"/>
-      <c r="T9" s="40" t="n"/>
-      <c r="U9" s="40" t="n"/>
-      <c r="V9" s="40" t="n"/>
-      <c r="W9" s="40" t="n"/>
-      <c r="X9" s="39" t="inlineStr">
+      <c r="O9" s="41" t="n"/>
+      <c r="P9" s="41" t="n"/>
+      <c r="Q9" s="41" t="n"/>
+      <c r="R9" s="41" t="n"/>
+      <c r="S9" s="41" t="n"/>
+      <c r="T9" s="41" t="n"/>
+      <c r="U9" s="41" t="n"/>
+      <c r="V9" s="41" t="n"/>
+      <c r="W9" s="41" t="n"/>
+      <c r="X9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="Y9" s="40" t="n"/>
-      <c r="Z9" s="40" t="n"/>
-      <c r="AA9" s="40" t="n"/>
-      <c r="AB9" s="40" t="n"/>
-      <c r="AC9" s="40" t="n"/>
-      <c r="AD9" s="40" t="n"/>
-      <c r="AE9" s="40" t="n"/>
-      <c r="AF9" s="40" t="n"/>
-      <c r="AG9" s="40" t="n"/>
-      <c r="AH9" s="39" t="inlineStr">
+      <c r="Y9" s="41" t="n"/>
+      <c r="Z9" s="41" t="n"/>
+      <c r="AA9" s="41" t="n"/>
+      <c r="AB9" s="41" t="n"/>
+      <c r="AC9" s="41" t="n"/>
+      <c r="AD9" s="41" t="n"/>
+      <c r="AE9" s="41" t="n"/>
+      <c r="AF9" s="41" t="n"/>
+      <c r="AG9" s="41" t="n"/>
+      <c r="AH9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AI9" s="40" t="n"/>
-      <c r="AJ9" s="40" t="n"/>
-      <c r="AK9" s="40" t="n"/>
-      <c r="AL9" s="40" t="n"/>
-      <c r="AM9" s="40" t="n"/>
-      <c r="AN9" s="40" t="n"/>
-      <c r="AO9" s="40" t="n"/>
-      <c r="AP9" s="40" t="n"/>
-      <c r="AQ9" s="40" t="n"/>
-      <c r="AR9" s="39" t="inlineStr">
+      <c r="AI9" s="41" t="n"/>
+      <c r="AJ9" s="41" t="n"/>
+      <c r="AK9" s="41" t="n"/>
+      <c r="AL9" s="41" t="n"/>
+      <c r="AM9" s="41" t="n"/>
+      <c r="AN9" s="41" t="n"/>
+      <c r="AO9" s="41" t="n"/>
+      <c r="AP9" s="41" t="n"/>
+      <c r="AQ9" s="41" t="n"/>
+      <c r="AR9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AS9" s="40" t="n"/>
-      <c r="AT9" s="40" t="n"/>
-      <c r="AU9" s="40" t="n"/>
-      <c r="AV9" s="40" t="n"/>
-      <c r="AW9" s="40" t="n"/>
-      <c r="AX9" s="40" t="n"/>
-      <c r="AY9" s="40" t="n"/>
-      <c r="AZ9" s="40" t="n"/>
-      <c r="BA9" s="40" t="n"/>
-      <c r="BB9" s="39" t="inlineStr">
+      <c r="AS9" s="41" t="n"/>
+      <c r="AT9" s="41" t="n"/>
+      <c r="AU9" s="41" t="n"/>
+      <c r="AV9" s="41" t="n"/>
+      <c r="AW9" s="41" t="n"/>
+      <c r="AX9" s="41" t="n"/>
+      <c r="AY9" s="41" t="n"/>
+      <c r="AZ9" s="41" t="n"/>
+      <c r="BA9" s="41" t="n"/>
+      <c r="BB9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BC9" s="40" t="n"/>
-      <c r="BD9" s="40" t="n"/>
-      <c r="BE9" s="40" t="n"/>
-      <c r="BF9" s="40" t="n"/>
-      <c r="BG9" s="40" t="n"/>
-      <c r="BH9" s="40" t="n"/>
-      <c r="BI9" s="40" t="n"/>
-      <c r="BJ9" s="40" t="n"/>
-      <c r="BK9" s="40" t="n"/>
-      <c r="BL9" s="39" t="inlineStr">
+      <c r="BC9" s="41" t="n"/>
+      <c r="BD9" s="41" t="n"/>
+      <c r="BE9" s="41" t="n"/>
+      <c r="BF9" s="41" t="n"/>
+      <c r="BG9" s="41" t="n"/>
+      <c r="BH9" s="41" t="n"/>
+      <c r="BI9" s="41" t="n"/>
+      <c r="BJ9" s="41" t="n"/>
+      <c r="BK9" s="41" t="n"/>
+      <c r="BL9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BM9" s="40" t="n"/>
-      <c r="BN9" s="40" t="n"/>
-      <c r="BO9" s="40" t="n"/>
-      <c r="BP9" s="40" t="n"/>
-      <c r="BQ9" s="40" t="n"/>
-      <c r="BR9" s="40" t="n"/>
-      <c r="BS9" s="40" t="n"/>
-      <c r="BT9" s="40" t="n"/>
-      <c r="BU9" s="40" t="n"/>
-      <c r="BV9" s="39" t="inlineStr">
+      <c r="BM9" s="41" t="n"/>
+      <c r="BN9" s="41" t="n"/>
+      <c r="BO9" s="41" t="n"/>
+      <c r="BP9" s="41" t="n"/>
+      <c r="BQ9" s="41" t="n"/>
+      <c r="BR9" s="41" t="n"/>
+      <c r="BS9" s="41" t="n"/>
+      <c r="BT9" s="41" t="n"/>
+      <c r="BU9" s="41" t="n"/>
+      <c r="BV9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BW9" s="40" t="n"/>
-      <c r="BX9" s="40" t="n"/>
-      <c r="BY9" s="40" t="n"/>
-      <c r="BZ9" s="40" t="n"/>
-      <c r="CA9" s="40" t="n"/>
-      <c r="CB9" s="40" t="n"/>
-      <c r="CC9" s="40" t="n"/>
-      <c r="CD9" s="40" t="n"/>
-      <c r="CE9" s="40" t="n"/>
-      <c r="CF9" s="39" t="inlineStr">
+      <c r="BW9" s="41" t="n"/>
+      <c r="BX9" s="41" t="n"/>
+      <c r="BY9" s="41" t="n"/>
+      <c r="BZ9" s="41" t="n"/>
+      <c r="CA9" s="41" t="n"/>
+      <c r="CB9" s="41" t="n"/>
+      <c r="CC9" s="41" t="n"/>
+      <c r="CD9" s="41" t="n"/>
+      <c r="CE9" s="41" t="n"/>
+      <c r="CF9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CG9" s="40" t="n"/>
-      <c r="CH9" s="40" t="n"/>
-      <c r="CI9" s="40" t="n"/>
-      <c r="CJ9" s="40" t="n"/>
-      <c r="CK9" s="40" t="n"/>
-      <c r="CL9" s="40" t="n"/>
-      <c r="CM9" s="40" t="n"/>
-      <c r="CN9" s="40" t="n"/>
-      <c r="CO9" s="40" t="n"/>
-      <c r="CP9" s="39" t="inlineStr">
+      <c r="CG9" s="41" t="n"/>
+      <c r="CH9" s="41" t="n"/>
+      <c r="CI9" s="41" t="n"/>
+      <c r="CJ9" s="41" t="n"/>
+      <c r="CK9" s="41" t="n"/>
+      <c r="CL9" s="41" t="n"/>
+      <c r="CM9" s="41" t="n"/>
+      <c r="CN9" s="41" t="n"/>
+      <c r="CO9" s="41" t="n"/>
+      <c r="CP9" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CQ9" s="40" t="n"/>
-      <c r="CR9" s="40" t="n"/>
-      <c r="CS9" s="40" t="n"/>
-      <c r="CT9" s="40" t="n"/>
-      <c r="CU9" s="40" t="n"/>
-      <c r="CV9" s="40" t="n"/>
-      <c r="CW9" s="40" t="n"/>
-      <c r="CX9" s="40" t="n"/>
-      <c r="CY9" s="40" t="n"/>
-      <c r="CZ9" s="41" t="n"/>
+      <c r="CQ9" s="41" t="n"/>
+      <c r="CR9" s="41" t="n"/>
+      <c r="CS9" s="41" t="n"/>
+      <c r="CT9" s="41" t="n"/>
+      <c r="CU9" s="41" t="n"/>
+      <c r="CV9" s="41" t="n"/>
+      <c r="CW9" s="41" t="n"/>
+      <c r="CX9" s="41" t="n"/>
+      <c r="CY9" s="41" t="n"/>
+      <c r="CZ9" s="42" t="n"/>
     </row>
     <row r="10" ht="4" customHeight="1"/>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Cont. 3</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
-        <is>
-          <t>99.3%</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>96.1%</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D11" s="39" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="E11" s="40" t="n"/>
-      <c r="F11" s="40" t="n"/>
-      <c r="G11" s="40" t="n"/>
-      <c r="H11" s="40" t="n"/>
-      <c r="I11" s="40" t="n"/>
-      <c r="J11" s="40" t="n"/>
-      <c r="K11" s="40" t="n"/>
-      <c r="L11" s="40" t="n"/>
-      <c r="M11" s="40" t="n"/>
-      <c r="N11" s="39" t="inlineStr">
+      <c r="E11" s="41" t="n"/>
+      <c r="F11" s="41" t="n"/>
+      <c r="G11" s="41" t="n"/>
+      <c r="H11" s="41" t="n"/>
+      <c r="I11" s="41" t="n"/>
+      <c r="J11" s="41" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="41" t="n"/>
+      <c r="M11" s="41" t="n"/>
+      <c r="N11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="O11" s="40" t="n"/>
-      <c r="P11" s="40" t="n"/>
-      <c r="Q11" s="40" t="n"/>
-      <c r="R11" s="40" t="n"/>
-      <c r="S11" s="40" t="n"/>
-      <c r="T11" s="40" t="n"/>
-      <c r="U11" s="40" t="n"/>
-      <c r="V11" s="40" t="n"/>
-      <c r="W11" s="40" t="n"/>
-      <c r="X11" s="39" t="inlineStr">
+      <c r="O11" s="41" t="n"/>
+      <c r="P11" s="41" t="n"/>
+      <c r="Q11" s="41" t="n"/>
+      <c r="R11" s="41" t="n"/>
+      <c r="S11" s="41" t="n"/>
+      <c r="T11" s="41" t="n"/>
+      <c r="U11" s="41" t="n"/>
+      <c r="V11" s="41" t="n"/>
+      <c r="W11" s="41" t="n"/>
+      <c r="X11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="Y11" s="40" t="n"/>
-      <c r="Z11" s="40" t="n"/>
-      <c r="AA11" s="40" t="n"/>
-      <c r="AB11" s="40" t="n"/>
-      <c r="AC11" s="40" t="n"/>
-      <c r="AD11" s="40" t="n"/>
-      <c r="AE11" s="40" t="n"/>
-      <c r="AF11" s="40" t="n"/>
-      <c r="AG11" s="40" t="n"/>
-      <c r="AH11" s="39" t="inlineStr">
+      <c r="Y11" s="41" t="n"/>
+      <c r="Z11" s="41" t="n"/>
+      <c r="AA11" s="41" t="n"/>
+      <c r="AB11" s="41" t="n"/>
+      <c r="AC11" s="41" t="n"/>
+      <c r="AD11" s="41" t="n"/>
+      <c r="AE11" s="41" t="n"/>
+      <c r="AF11" s="41" t="n"/>
+      <c r="AG11" s="41" t="n"/>
+      <c r="AH11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AI11" s="40" t="n"/>
-      <c r="AJ11" s="40" t="n"/>
-      <c r="AK11" s="40" t="n"/>
-      <c r="AL11" s="40" t="n"/>
-      <c r="AM11" s="40" t="n"/>
-      <c r="AN11" s="40" t="n"/>
-      <c r="AO11" s="40" t="n"/>
-      <c r="AP11" s="40" t="n"/>
-      <c r="AQ11" s="40" t="n"/>
-      <c r="AR11" s="39" t="inlineStr">
+      <c r="AI11" s="41" t="n"/>
+      <c r="AJ11" s="41" t="n"/>
+      <c r="AK11" s="41" t="n"/>
+      <c r="AL11" s="41" t="n"/>
+      <c r="AM11" s="41" t="n"/>
+      <c r="AN11" s="41" t="n"/>
+      <c r="AO11" s="41" t="n"/>
+      <c r="AP11" s="41" t="n"/>
+      <c r="AQ11" s="41" t="n"/>
+      <c r="AR11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AS11" s="40" t="n"/>
-      <c r="AT11" s="40" t="n"/>
-      <c r="AU11" s="40" t="n"/>
-      <c r="AV11" s="40" t="n"/>
-      <c r="AW11" s="40" t="n"/>
-      <c r="AX11" s="40" t="n"/>
-      <c r="AY11" s="40" t="n"/>
-      <c r="AZ11" s="40" t="n"/>
-      <c r="BA11" s="40" t="n"/>
-      <c r="BB11" s="39" t="inlineStr">
+      <c r="AS11" s="41" t="n"/>
+      <c r="AT11" s="41" t="n"/>
+      <c r="AU11" s="41" t="n"/>
+      <c r="AV11" s="41" t="n"/>
+      <c r="AW11" s="41" t="n"/>
+      <c r="AX11" s="41" t="n"/>
+      <c r="AY11" s="41" t="n"/>
+      <c r="AZ11" s="41" t="n"/>
+      <c r="BA11" s="41" t="n"/>
+      <c r="BB11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BC11" s="40" t="n"/>
-      <c r="BD11" s="40" t="n"/>
-      <c r="BE11" s="40" t="n"/>
-      <c r="BF11" s="40" t="n"/>
-      <c r="BG11" s="40" t="n"/>
-      <c r="BH11" s="40" t="n"/>
-      <c r="BI11" s="40" t="n"/>
-      <c r="BJ11" s="40" t="n"/>
-      <c r="BK11" s="40" t="n"/>
-      <c r="BL11" s="39" t="inlineStr">
+      <c r="BC11" s="41" t="n"/>
+      <c r="BD11" s="41" t="n"/>
+      <c r="BE11" s="41" t="n"/>
+      <c r="BF11" s="41" t="n"/>
+      <c r="BG11" s="41" t="n"/>
+      <c r="BH11" s="41" t="n"/>
+      <c r="BI11" s="41" t="n"/>
+      <c r="BJ11" s="41" t="n"/>
+      <c r="BK11" s="41" t="n"/>
+      <c r="BL11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BM11" s="40" t="n"/>
-      <c r="BN11" s="40" t="n"/>
-      <c r="BO11" s="40" t="n"/>
-      <c r="BP11" s="40" t="n"/>
-      <c r="BQ11" s="40" t="n"/>
-      <c r="BR11" s="40" t="n"/>
-      <c r="BS11" s="40" t="n"/>
-      <c r="BT11" s="40" t="n"/>
-      <c r="BU11" s="40" t="n"/>
-      <c r="BV11" s="39" t="inlineStr">
+      <c r="BM11" s="41" t="n"/>
+      <c r="BN11" s="41" t="n"/>
+      <c r="BO11" s="41" t="n"/>
+      <c r="BP11" s="41" t="n"/>
+      <c r="BQ11" s="41" t="n"/>
+      <c r="BR11" s="41" t="n"/>
+      <c r="BS11" s="41" t="n"/>
+      <c r="BT11" s="41" t="n"/>
+      <c r="BU11" s="41" t="n"/>
+      <c r="BV11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BW11" s="40" t="n"/>
-      <c r="BX11" s="40" t="n"/>
-      <c r="BY11" s="40" t="n"/>
-      <c r="BZ11" s="40" t="n"/>
-      <c r="CA11" s="40" t="n"/>
-      <c r="CB11" s="40" t="n"/>
-      <c r="CC11" s="40" t="n"/>
-      <c r="CD11" s="40" t="n"/>
-      <c r="CE11" s="40" t="n"/>
-      <c r="CF11" s="39" t="inlineStr">
+      <c r="BW11" s="41" t="n"/>
+      <c r="BX11" s="41" t="n"/>
+      <c r="BY11" s="41" t="n"/>
+      <c r="BZ11" s="41" t="n"/>
+      <c r="CA11" s="41" t="n"/>
+      <c r="CB11" s="41" t="n"/>
+      <c r="CC11" s="41" t="n"/>
+      <c r="CD11" s="41" t="n"/>
+      <c r="CE11" s="41" t="n"/>
+      <c r="CF11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CG11" s="40" t="n"/>
-      <c r="CH11" s="40" t="n"/>
-      <c r="CI11" s="40" t="n"/>
-      <c r="CJ11" s="40" t="n"/>
-      <c r="CK11" s="40" t="n"/>
-      <c r="CL11" s="40" t="n"/>
-      <c r="CM11" s="40" t="n"/>
-      <c r="CN11" s="40" t="n"/>
-      <c r="CO11" s="40" t="n"/>
-      <c r="CP11" s="39" t="inlineStr">
+      <c r="CG11" s="41" t="n"/>
+      <c r="CH11" s="41" t="n"/>
+      <c r="CI11" s="41" t="n"/>
+      <c r="CJ11" s="41" t="n"/>
+      <c r="CK11" s="41" t="n"/>
+      <c r="CL11" s="41" t="n"/>
+      <c r="CM11" s="41" t="n"/>
+      <c r="CN11" s="41" t="n"/>
+      <c r="CO11" s="41" t="n"/>
+      <c r="CP11" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CQ11" s="40" t="n"/>
-      <c r="CR11" s="40" t="n"/>
-      <c r="CS11" s="40" t="n"/>
-      <c r="CT11" s="40" t="n"/>
-      <c r="CU11" s="40" t="n"/>
-      <c r="CV11" s="40" t="n"/>
-      <c r="CW11" s="40" t="n"/>
-      <c r="CX11" s="40" t="n"/>
-      <c r="CY11" s="40" t="n"/>
-      <c r="CZ11" s="41" t="n"/>
+      <c r="CQ11" s="41" t="n"/>
+      <c r="CR11" s="41" t="n"/>
+      <c r="CS11" s="41" t="n"/>
+      <c r="CT11" s="41" t="n"/>
+      <c r="CU11" s="41" t="n"/>
+      <c r="CV11" s="41" t="n"/>
+      <c r="CW11" s="41" t="n"/>
+      <c r="CX11" s="41" t="n"/>
+      <c r="CY11" s="41" t="n"/>
+      <c r="CZ11" s="42" t="n"/>
     </row>
     <row r="12" ht="4" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Cont. 4</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>99.3%</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>96.6%</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D13" s="39" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="E13" s="40" t="n"/>
-      <c r="F13" s="40" t="n"/>
-      <c r="G13" s="40" t="n"/>
-      <c r="H13" s="40" t="n"/>
-      <c r="I13" s="40" t="n"/>
-      <c r="J13" s="40" t="n"/>
-      <c r="K13" s="40" t="n"/>
-      <c r="L13" s="40" t="n"/>
-      <c r="M13" s="40" t="n"/>
-      <c r="N13" s="39" t="inlineStr">
+      <c r="E13" s="41" t="n"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="G13" s="41" t="n"/>
+      <c r="H13" s="41" t="n"/>
+      <c r="I13" s="41" t="n"/>
+      <c r="J13" s="41" t="n"/>
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="41" t="n"/>
+      <c r="M13" s="41" t="n"/>
+      <c r="N13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="O13" s="40" t="n"/>
-      <c r="P13" s="40" t="n"/>
-      <c r="Q13" s="40" t="n"/>
-      <c r="R13" s="40" t="n"/>
-      <c r="S13" s="40" t="n"/>
-      <c r="T13" s="40" t="n"/>
-      <c r="U13" s="40" t="n"/>
-      <c r="V13" s="40" t="n"/>
-      <c r="W13" s="40" t="n"/>
-      <c r="X13" s="39" t="inlineStr">
+      <c r="O13" s="41" t="n"/>
+      <c r="P13" s="41" t="n"/>
+      <c r="Q13" s="41" t="n"/>
+      <c r="R13" s="41" t="n"/>
+      <c r="S13" s="41" t="n"/>
+      <c r="T13" s="41" t="n"/>
+      <c r="U13" s="41" t="n"/>
+      <c r="V13" s="41" t="n"/>
+      <c r="W13" s="41" t="n"/>
+      <c r="X13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="Y13" s="40" t="n"/>
-      <c r="Z13" s="40" t="n"/>
-      <c r="AA13" s="40" t="n"/>
-      <c r="AB13" s="40" t="n"/>
-      <c r="AC13" s="40" t="n"/>
-      <c r="AD13" s="40" t="n"/>
-      <c r="AE13" s="40" t="n"/>
-      <c r="AF13" s="40" t="n"/>
-      <c r="AG13" s="40" t="n"/>
-      <c r="AH13" s="39" t="inlineStr">
+      <c r="Y13" s="41" t="n"/>
+      <c r="Z13" s="41" t="n"/>
+      <c r="AA13" s="41" t="n"/>
+      <c r="AB13" s="41" t="n"/>
+      <c r="AC13" s="41" t="n"/>
+      <c r="AD13" s="41" t="n"/>
+      <c r="AE13" s="41" t="n"/>
+      <c r="AF13" s="41" t="n"/>
+      <c r="AG13" s="41" t="n"/>
+      <c r="AH13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AI13" s="40" t="n"/>
-      <c r="AJ13" s="40" t="n"/>
-      <c r="AK13" s="40" t="n"/>
-      <c r="AL13" s="40" t="n"/>
-      <c r="AM13" s="40" t="n"/>
-      <c r="AN13" s="40" t="n"/>
-      <c r="AO13" s="40" t="n"/>
-      <c r="AP13" s="40" t="n"/>
-      <c r="AQ13" s="40" t="n"/>
-      <c r="AR13" s="39" t="inlineStr">
+      <c r="AI13" s="41" t="n"/>
+      <c r="AJ13" s="41" t="n"/>
+      <c r="AK13" s="41" t="n"/>
+      <c r="AL13" s="41" t="n"/>
+      <c r="AM13" s="41" t="n"/>
+      <c r="AN13" s="41" t="n"/>
+      <c r="AO13" s="41" t="n"/>
+      <c r="AP13" s="41" t="n"/>
+      <c r="AQ13" s="41" t="n"/>
+      <c r="AR13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AS13" s="40" t="n"/>
-      <c r="AT13" s="40" t="n"/>
-      <c r="AU13" s="40" t="n"/>
-      <c r="AV13" s="40" t="n"/>
-      <c r="AW13" s="40" t="n"/>
-      <c r="AX13" s="40" t="n"/>
-      <c r="AY13" s="40" t="n"/>
-      <c r="AZ13" s="40" t="n"/>
-      <c r="BA13" s="40" t="n"/>
-      <c r="BB13" s="39" t="inlineStr">
+      <c r="AS13" s="41" t="n"/>
+      <c r="AT13" s="41" t="n"/>
+      <c r="AU13" s="41" t="n"/>
+      <c r="AV13" s="41" t="n"/>
+      <c r="AW13" s="41" t="n"/>
+      <c r="AX13" s="41" t="n"/>
+      <c r="AY13" s="41" t="n"/>
+      <c r="AZ13" s="41" t="n"/>
+      <c r="BA13" s="41" t="n"/>
+      <c r="BB13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BC13" s="40" t="n"/>
-      <c r="BD13" s="40" t="n"/>
-      <c r="BE13" s="40" t="n"/>
-      <c r="BF13" s="40" t="n"/>
-      <c r="BG13" s="40" t="n"/>
-      <c r="BH13" s="40" t="n"/>
-      <c r="BI13" s="40" t="n"/>
-      <c r="BJ13" s="40" t="n"/>
-      <c r="BK13" s="40" t="n"/>
-      <c r="BL13" s="39" t="inlineStr">
+      <c r="BC13" s="41" t="n"/>
+      <c r="BD13" s="41" t="n"/>
+      <c r="BE13" s="41" t="n"/>
+      <c r="BF13" s="41" t="n"/>
+      <c r="BG13" s="41" t="n"/>
+      <c r="BH13" s="41" t="n"/>
+      <c r="BI13" s="41" t="n"/>
+      <c r="BJ13" s="41" t="n"/>
+      <c r="BK13" s="41" t="n"/>
+      <c r="BL13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BM13" s="40" t="n"/>
-      <c r="BN13" s="40" t="n"/>
-      <c r="BO13" s="40" t="n"/>
-      <c r="BP13" s="40" t="n"/>
-      <c r="BQ13" s="40" t="n"/>
-      <c r="BR13" s="40" t="n"/>
-      <c r="BS13" s="40" t="n"/>
-      <c r="BT13" s="40" t="n"/>
-      <c r="BU13" s="40" t="n"/>
-      <c r="BV13" s="39" t="inlineStr">
+      <c r="BM13" s="41" t="n"/>
+      <c r="BN13" s="41" t="n"/>
+      <c r="BO13" s="41" t="n"/>
+      <c r="BP13" s="41" t="n"/>
+      <c r="BQ13" s="41" t="n"/>
+      <c r="BR13" s="41" t="n"/>
+      <c r="BS13" s="41" t="n"/>
+      <c r="BT13" s="41" t="n"/>
+      <c r="BU13" s="41" t="n"/>
+      <c r="BV13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BW13" s="40" t="n"/>
-      <c r="BX13" s="40" t="n"/>
-      <c r="BY13" s="40" t="n"/>
-      <c r="BZ13" s="40" t="n"/>
-      <c r="CA13" s="40" t="n"/>
-      <c r="CB13" s="40" t="n"/>
-      <c r="CC13" s="40" t="n"/>
-      <c r="CD13" s="40" t="n"/>
-      <c r="CE13" s="40" t="n"/>
-      <c r="CF13" s="39" t="inlineStr">
+      <c r="BW13" s="41" t="n"/>
+      <c r="BX13" s="41" t="n"/>
+      <c r="BY13" s="41" t="n"/>
+      <c r="BZ13" s="41" t="n"/>
+      <c r="CA13" s="41" t="n"/>
+      <c r="CB13" s="41" t="n"/>
+      <c r="CC13" s="41" t="n"/>
+      <c r="CD13" s="41" t="n"/>
+      <c r="CE13" s="41" t="n"/>
+      <c r="CF13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CG13" s="40" t="n"/>
-      <c r="CH13" s="40" t="n"/>
-      <c r="CI13" s="40" t="n"/>
-      <c r="CJ13" s="40" t="n"/>
-      <c r="CK13" s="40" t="n"/>
-      <c r="CL13" s="40" t="n"/>
-      <c r="CM13" s="40" t="n"/>
-      <c r="CN13" s="40" t="n"/>
-      <c r="CO13" s="40" t="n"/>
-      <c r="CP13" s="39" t="inlineStr">
+      <c r="CG13" s="41" t="n"/>
+      <c r="CH13" s="41" t="n"/>
+      <c r="CI13" s="41" t="n"/>
+      <c r="CJ13" s="41" t="n"/>
+      <c r="CK13" s="41" t="n"/>
+      <c r="CL13" s="41" t="n"/>
+      <c r="CM13" s="41" t="n"/>
+      <c r="CN13" s="41" t="n"/>
+      <c r="CO13" s="41" t="n"/>
+      <c r="CP13" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CQ13" s="40" t="n"/>
-      <c r="CR13" s="40" t="n"/>
-      <c r="CS13" s="40" t="n"/>
-      <c r="CT13" s="40" t="n"/>
-      <c r="CU13" s="40" t="n"/>
-      <c r="CV13" s="40" t="n"/>
-      <c r="CW13" s="40" t="n"/>
-      <c r="CX13" s="40" t="n"/>
-      <c r="CY13" s="40" t="n"/>
-      <c r="CZ13" s="41" t="n"/>
+      <c r="CQ13" s="41" t="n"/>
+      <c r="CR13" s="41" t="n"/>
+      <c r="CS13" s="41" t="n"/>
+      <c r="CT13" s="41" t="n"/>
+      <c r="CU13" s="41" t="n"/>
+      <c r="CV13" s="41" t="n"/>
+      <c r="CW13" s="41" t="n"/>
+      <c r="CX13" s="41" t="n"/>
+      <c r="CY13" s="41" t="n"/>
+      <c r="CZ13" s="42" t="n"/>
     </row>
     <row r="14" ht="4" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Cont. 5</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>99.3%</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>93.4%</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D15" s="39" t="inlineStr">
+      <c r="D15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="E15" s="40" t="n"/>
-      <c r="F15" s="40" t="n"/>
-      <c r="G15" s="40" t="n"/>
-      <c r="H15" s="40" t="n"/>
-      <c r="I15" s="40" t="n"/>
-      <c r="J15" s="40" t="n"/>
-      <c r="K15" s="40" t="n"/>
-      <c r="L15" s="40" t="n"/>
-      <c r="M15" s="40" t="n"/>
-      <c r="N15" s="39" t="inlineStr">
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="41" t="n"/>
+      <c r="G15" s="41" t="n"/>
+      <c r="H15" s="41" t="n"/>
+      <c r="I15" s="41" t="n"/>
+      <c r="J15" s="41" t="n"/>
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="41" t="n"/>
+      <c r="M15" s="41" t="n"/>
+      <c r="N15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="O15" s="40" t="n"/>
-      <c r="P15" s="40" t="n"/>
-      <c r="Q15" s="40" t="n"/>
-      <c r="R15" s="40" t="n"/>
-      <c r="S15" s="40" t="n"/>
-      <c r="T15" s="40" t="n"/>
-      <c r="U15" s="40" t="n"/>
-      <c r="V15" s="40" t="n"/>
-      <c r="W15" s="40" t="n"/>
-      <c r="X15" s="39" t="inlineStr">
+      <c r="O15" s="41" t="n"/>
+      <c r="P15" s="41" t="n"/>
+      <c r="Q15" s="41" t="n"/>
+      <c r="R15" s="41" t="n"/>
+      <c r="S15" s="41" t="n"/>
+      <c r="T15" s="41" t="n"/>
+      <c r="U15" s="41" t="n"/>
+      <c r="V15" s="41" t="n"/>
+      <c r="W15" s="41" t="n"/>
+      <c r="X15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="Y15" s="40" t="n"/>
-      <c r="Z15" s="40" t="n"/>
-      <c r="AA15" s="40" t="n"/>
-      <c r="AB15" s="40" t="n"/>
-      <c r="AC15" s="40" t="n"/>
-      <c r="AD15" s="40" t="n"/>
-      <c r="AE15" s="40" t="n"/>
-      <c r="AF15" s="40" t="n"/>
-      <c r="AG15" s="40" t="n"/>
-      <c r="AH15" s="39" t="inlineStr">
+      <c r="Y15" s="41" t="n"/>
+      <c r="Z15" s="41" t="n"/>
+      <c r="AA15" s="41" t="n"/>
+      <c r="AB15" s="41" t="n"/>
+      <c r="AC15" s="41" t="n"/>
+      <c r="AD15" s="41" t="n"/>
+      <c r="AE15" s="41" t="n"/>
+      <c r="AF15" s="41" t="n"/>
+      <c r="AG15" s="41" t="n"/>
+      <c r="AH15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AI15" s="40" t="n"/>
-      <c r="AJ15" s="40" t="n"/>
-      <c r="AK15" s="40" t="n"/>
-      <c r="AL15" s="40" t="n"/>
-      <c r="AM15" s="40" t="n"/>
-      <c r="AN15" s="40" t="n"/>
-      <c r="AO15" s="40" t="n"/>
-      <c r="AP15" s="40" t="n"/>
-      <c r="AQ15" s="40" t="n"/>
-      <c r="AR15" s="39" t="inlineStr">
+      <c r="AI15" s="41" t="n"/>
+      <c r="AJ15" s="41" t="n"/>
+      <c r="AK15" s="41" t="n"/>
+      <c r="AL15" s="41" t="n"/>
+      <c r="AM15" s="41" t="n"/>
+      <c r="AN15" s="41" t="n"/>
+      <c r="AO15" s="41" t="n"/>
+      <c r="AP15" s="41" t="n"/>
+      <c r="AQ15" s="41" t="n"/>
+      <c r="AR15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="AS15" s="40" t="n"/>
-      <c r="AT15" s="40" t="n"/>
-      <c r="AU15" s="40" t="n"/>
-      <c r="AV15" s="40" t="n"/>
-      <c r="AW15" s="40" t="n"/>
-      <c r="AX15" s="40" t="n"/>
-      <c r="AY15" s="40" t="n"/>
-      <c r="AZ15" s="40" t="n"/>
-      <c r="BA15" s="40" t="n"/>
-      <c r="BB15" s="39" t="inlineStr">
+      <c r="AS15" s="41" t="n"/>
+      <c r="AT15" s="41" t="n"/>
+      <c r="AU15" s="41" t="n"/>
+      <c r="AV15" s="41" t="n"/>
+      <c r="AW15" s="41" t="n"/>
+      <c r="AX15" s="41" t="n"/>
+      <c r="AY15" s="41" t="n"/>
+      <c r="AZ15" s="41" t="n"/>
+      <c r="BA15" s="41" t="n"/>
+      <c r="BB15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BC15" s="40" t="n"/>
-      <c r="BD15" s="40" t="n"/>
-      <c r="BE15" s="40" t="n"/>
-      <c r="BF15" s="40" t="n"/>
-      <c r="BG15" s="40" t="n"/>
-      <c r="BH15" s="40" t="n"/>
-      <c r="BI15" s="40" t="n"/>
-      <c r="BJ15" s="40" t="n"/>
-      <c r="BK15" s="40" t="n"/>
-      <c r="BL15" s="39" t="inlineStr">
+      <c r="BC15" s="41" t="n"/>
+      <c r="BD15" s="41" t="n"/>
+      <c r="BE15" s="41" t="n"/>
+      <c r="BF15" s="41" t="n"/>
+      <c r="BG15" s="41" t="n"/>
+      <c r="BH15" s="41" t="n"/>
+      <c r="BI15" s="41" t="n"/>
+      <c r="BJ15" s="41" t="n"/>
+      <c r="BK15" s="41" t="n"/>
+      <c r="BL15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BM15" s="40" t="n"/>
-      <c r="BN15" s="40" t="n"/>
-      <c r="BO15" s="40" t="n"/>
-      <c r="BP15" s="40" t="n"/>
-      <c r="BQ15" s="40" t="n"/>
-      <c r="BR15" s="40" t="n"/>
-      <c r="BS15" s="40" t="n"/>
-      <c r="BT15" s="40" t="n"/>
-      <c r="BU15" s="40" t="n"/>
-      <c r="BV15" s="39" t="inlineStr">
+      <c r="BM15" s="41" t="n"/>
+      <c r="BN15" s="41" t="n"/>
+      <c r="BO15" s="41" t="n"/>
+      <c r="BP15" s="41" t="n"/>
+      <c r="BQ15" s="41" t="n"/>
+      <c r="BR15" s="41" t="n"/>
+      <c r="BS15" s="41" t="n"/>
+      <c r="BT15" s="41" t="n"/>
+      <c r="BU15" s="41" t="n"/>
+      <c r="BV15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="BW15" s="40" t="n"/>
-      <c r="BX15" s="40" t="n"/>
-      <c r="BY15" s="40" t="n"/>
-      <c r="BZ15" s="40" t="n"/>
-      <c r="CA15" s="40" t="n"/>
-      <c r="CB15" s="40" t="n"/>
-      <c r="CC15" s="40" t="n"/>
-      <c r="CD15" s="40" t="n"/>
-      <c r="CE15" s="40" t="n"/>
-      <c r="CF15" s="39" t="inlineStr">
+      <c r="BW15" s="41" t="n"/>
+      <c r="BX15" s="41" t="n"/>
+      <c r="BY15" s="41" t="n"/>
+      <c r="BZ15" s="41" t="n"/>
+      <c r="CA15" s="41" t="n"/>
+      <c r="CB15" s="41" t="n"/>
+      <c r="CC15" s="41" t="n"/>
+      <c r="CD15" s="41" t="n"/>
+      <c r="CE15" s="41" t="n"/>
+      <c r="CF15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CG15" s="40" t="n"/>
-      <c r="CH15" s="40" t="n"/>
-      <c r="CI15" s="40" t="n"/>
-      <c r="CJ15" s="40" t="n"/>
-      <c r="CK15" s="40" t="n"/>
-      <c r="CL15" s="40" t="n"/>
-      <c r="CM15" s="40" t="n"/>
-      <c r="CN15" s="40" t="n"/>
-      <c r="CO15" s="40" t="n"/>
-      <c r="CP15" s="39" t="inlineStr">
+      <c r="CG15" s="41" t="n"/>
+      <c r="CH15" s="41" t="n"/>
+      <c r="CI15" s="41" t="n"/>
+      <c r="CJ15" s="41" t="n"/>
+      <c r="CK15" s="41" t="n"/>
+      <c r="CL15" s="41" t="n"/>
+      <c r="CM15" s="41" t="n"/>
+      <c r="CN15" s="41" t="n"/>
+      <c r="CO15" s="41" t="n"/>
+      <c r="CP15" s="40" t="inlineStr">
         <is>
           <t>115x115(4p)</t>
         </is>
       </c>
-      <c r="CQ15" s="40" t="n"/>
-      <c r="CR15" s="40" t="n"/>
-      <c r="CS15" s="40" t="n"/>
-      <c r="CT15" s="40" t="n"/>
-      <c r="CU15" s="40" t="n"/>
-      <c r="CV15" s="40" t="n"/>
-      <c r="CW15" s="40" t="n"/>
-      <c r="CX15" s="40" t="n"/>
-      <c r="CY15" s="40" t="n"/>
-      <c r="CZ15" s="41" t="n"/>
+      <c r="CQ15" s="41" t="n"/>
+      <c r="CR15" s="41" t="n"/>
+      <c r="CS15" s="41" t="n"/>
+      <c r="CT15" s="41" t="n"/>
+      <c r="CU15" s="41" t="n"/>
+      <c r="CV15" s="41" t="n"/>
+      <c r="CW15" s="41" t="n"/>
+      <c r="CX15" s="41" t="n"/>
+      <c r="CY15" s="41" t="n"/>
+      <c r="CZ15" s="42" t="n"/>
     </row>
     <row r="16" ht="4" customHeight="1"/>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>Cont. 6</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>95.0%</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
+        <is>
+          <t>64.8%</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D17" s="37" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="E17" s="38" t="n"/>
-      <c r="F17" s="38" t="n"/>
-      <c r="G17" s="38" t="n"/>
-      <c r="H17" s="38" t="n"/>
-      <c r="I17" s="38" t="n"/>
-      <c r="J17" s="37" t="inlineStr">
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
+      <c r="H17" s="39" t="n"/>
+      <c r="I17" s="39" t="n"/>
+      <c r="J17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="K17" s="38" t="n"/>
-      <c r="L17" s="38" t="n"/>
-      <c r="M17" s="38" t="n"/>
-      <c r="N17" s="38" t="n"/>
-      <c r="O17" s="38" t="n"/>
-      <c r="P17" s="38" t="n"/>
-      <c r="Q17" s="37" t="inlineStr">
+      <c r="K17" s="39" t="n"/>
+      <c r="L17" s="39" t="n"/>
+      <c r="M17" s="39" t="n"/>
+      <c r="N17" s="39" t="n"/>
+      <c r="O17" s="39" t="n"/>
+      <c r="P17" s="39" t="n"/>
+      <c r="Q17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="R17" s="38" t="n"/>
-      <c r="S17" s="38" t="n"/>
-      <c r="T17" s="38" t="n"/>
-      <c r="U17" s="38" t="n"/>
-      <c r="V17" s="38" t="n"/>
-      <c r="W17" s="38" t="n"/>
-      <c r="X17" s="37" t="inlineStr">
+      <c r="R17" s="39" t="n"/>
+      <c r="S17" s="39" t="n"/>
+      <c r="T17" s="39" t="n"/>
+      <c r="U17" s="39" t="n"/>
+      <c r="V17" s="39" t="n"/>
+      <c r="W17" s="39" t="n"/>
+      <c r="X17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="Y17" s="38" t="n"/>
-      <c r="Z17" s="38" t="n"/>
-      <c r="AA17" s="38" t="n"/>
-      <c r="AB17" s="38" t="n"/>
-      <c r="AC17" s="38" t="n"/>
-      <c r="AD17" s="38" t="n"/>
-      <c r="AE17" s="37" t="inlineStr">
+      <c r="Y17" s="39" t="n"/>
+      <c r="Z17" s="39" t="n"/>
+      <c r="AA17" s="39" t="n"/>
+      <c r="AB17" s="39" t="n"/>
+      <c r="AC17" s="39" t="n"/>
+      <c r="AD17" s="39" t="n"/>
+      <c r="AE17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AF17" s="38" t="n"/>
-      <c r="AG17" s="38" t="n"/>
-      <c r="AH17" s="38" t="n"/>
-      <c r="AI17" s="38" t="n"/>
-      <c r="AJ17" s="38" t="n"/>
-      <c r="AK17" s="38" t="n"/>
-      <c r="AL17" s="37" t="inlineStr">
+      <c r="AF17" s="39" t="n"/>
+      <c r="AG17" s="39" t="n"/>
+      <c r="AH17" s="39" t="n"/>
+      <c r="AI17" s="39" t="n"/>
+      <c r="AJ17" s="39" t="n"/>
+      <c r="AK17" s="39" t="n"/>
+      <c r="AL17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AM17" s="38" t="n"/>
-      <c r="AN17" s="38" t="n"/>
-      <c r="AO17" s="38" t="n"/>
-      <c r="AP17" s="38" t="n"/>
-      <c r="AQ17" s="38" t="n"/>
-      <c r="AR17" s="38" t="n"/>
-      <c r="AS17" s="37" t="inlineStr">
+      <c r="AM17" s="39" t="n"/>
+      <c r="AN17" s="39" t="n"/>
+      <c r="AO17" s="39" t="n"/>
+      <c r="AP17" s="39" t="n"/>
+      <c r="AQ17" s="39" t="n"/>
+      <c r="AR17" s="39" t="n"/>
+      <c r="AS17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AT17" s="38" t="n"/>
-      <c r="AU17" s="38" t="n"/>
-      <c r="AV17" s="38" t="n"/>
-      <c r="AW17" s="38" t="n"/>
-      <c r="AX17" s="38" t="n"/>
-      <c r="AY17" s="37" t="inlineStr">
+      <c r="AT17" s="39" t="n"/>
+      <c r="AU17" s="39" t="n"/>
+      <c r="AV17" s="39" t="n"/>
+      <c r="AW17" s="39" t="n"/>
+      <c r="AX17" s="39" t="n"/>
+      <c r="AY17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AZ17" s="38" t="n"/>
-      <c r="BA17" s="38" t="n"/>
-      <c r="BB17" s="38" t="n"/>
-      <c r="BC17" s="38" t="n"/>
-      <c r="BD17" s="38" t="n"/>
-      <c r="BE17" s="38" t="n"/>
-      <c r="BF17" s="37" t="inlineStr">
+      <c r="AZ17" s="39" t="n"/>
+      <c r="BA17" s="39" t="n"/>
+      <c r="BB17" s="39" t="n"/>
+      <c r="BC17" s="39" t="n"/>
+      <c r="BD17" s="39" t="n"/>
+      <c r="BE17" s="39" t="n"/>
+      <c r="BF17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BG17" s="38" t="n"/>
-      <c r="BH17" s="38" t="n"/>
-      <c r="BI17" s="38" t="n"/>
-      <c r="BJ17" s="38" t="n"/>
-      <c r="BK17" s="38" t="n"/>
-      <c r="BL17" s="38" t="n"/>
-      <c r="BM17" s="37" t="inlineStr">
+      <c r="BG17" s="39" t="n"/>
+      <c r="BH17" s="39" t="n"/>
+      <c r="BI17" s="39" t="n"/>
+      <c r="BJ17" s="39" t="n"/>
+      <c r="BK17" s="39" t="n"/>
+      <c r="BL17" s="39" t="n"/>
+      <c r="BM17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BN17" s="38" t="n"/>
-      <c r="BO17" s="38" t="n"/>
-      <c r="BP17" s="38" t="n"/>
-      <c r="BQ17" s="38" t="n"/>
-      <c r="BR17" s="38" t="n"/>
-      <c r="BS17" s="38" t="n"/>
-      <c r="BT17" s="37" t="inlineStr">
+      <c r="BN17" s="39" t="n"/>
+      <c r="BO17" s="39" t="n"/>
+      <c r="BP17" s="39" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
+      <c r="BR17" s="39" t="n"/>
+      <c r="BS17" s="39" t="n"/>
+      <c r="BT17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BU17" s="38" t="n"/>
-      <c r="BV17" s="38" t="n"/>
-      <c r="BW17" s="38" t="n"/>
-      <c r="BX17" s="38" t="n"/>
-      <c r="BY17" s="38" t="n"/>
-      <c r="BZ17" s="38" t="n"/>
-      <c r="CA17" s="37" t="inlineStr">
+      <c r="BU17" s="39" t="n"/>
+      <c r="BV17" s="39" t="n"/>
+      <c r="BW17" s="39" t="n"/>
+      <c r="BX17" s="39" t="n"/>
+      <c r="BY17" s="39" t="n"/>
+      <c r="BZ17" s="39" t="n"/>
+      <c r="CA17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CB17" s="38" t="n"/>
-      <c r="CC17" s="38" t="n"/>
-      <c r="CD17" s="38" t="n"/>
-      <c r="CE17" s="38" t="n"/>
-      <c r="CF17" s="38" t="n"/>
-      <c r="CG17" s="38" t="n"/>
-      <c r="CH17" s="37" t="inlineStr">
+      <c r="CB17" s="39" t="n"/>
+      <c r="CC17" s="39" t="n"/>
+      <c r="CD17" s="39" t="n"/>
+      <c r="CE17" s="39" t="n"/>
+      <c r="CF17" s="39" t="n"/>
+      <c r="CG17" s="39" t="n"/>
+      <c r="CH17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CI17" s="38" t="n"/>
-      <c r="CJ17" s="38" t="n"/>
-      <c r="CK17" s="38" t="n"/>
-      <c r="CL17" s="38" t="n"/>
-      <c r="CM17" s="38" t="n"/>
-      <c r="CN17" s="37" t="inlineStr">
+      <c r="CI17" s="39" t="n"/>
+      <c r="CJ17" s="39" t="n"/>
+      <c r="CK17" s="39" t="n"/>
+      <c r="CL17" s="39" t="n"/>
+      <c r="CM17" s="39" t="n"/>
+      <c r="CN17" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CO17" s="38" t="n"/>
-      <c r="CP17" s="38" t="n"/>
-      <c r="CQ17" s="38" t="n"/>
-      <c r="CR17" s="38" t="n"/>
-      <c r="CS17" s="38" t="n"/>
-      <c r="CT17" s="38" t="n"/>
-      <c r="CU17" s="38" t="n"/>
-      <c r="CV17" s="41" t="n"/>
-      <c r="CW17" s="41" t="n"/>
-      <c r="CX17" s="41" t="n"/>
-      <c r="CY17" s="41" t="n"/>
-      <c r="CZ17" s="41" t="n"/>
+      <c r="CO17" s="39" t="n"/>
+      <c r="CP17" s="39" t="n"/>
+      <c r="CQ17" s="39" t="n"/>
+      <c r="CR17" s="39" t="n"/>
+      <c r="CS17" s="39" t="n"/>
+      <c r="CT17" s="39" t="n"/>
+      <c r="CU17" s="39" t="n"/>
+      <c r="CV17" s="42" t="n"/>
+      <c r="CW17" s="42" t="n"/>
+      <c r="CX17" s="42" t="n"/>
+      <c r="CY17" s="42" t="n"/>
+      <c r="CZ17" s="42" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>NP Boxes</t>
         </is>
       </c>
-      <c r="D18" s="42" t="inlineStr">
+      <c r="D18" s="43" t="inlineStr">
         <is>
           <t>15b</t>
         </is>
       </c>
-      <c r="E18" s="43" t="n"/>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="43" t="n"/>
-      <c r="H18" s="43" t="n"/>
-      <c r="I18" s="43" t="n"/>
-      <c r="J18" s="42" t="inlineStr">
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="44" t="n"/>
+      <c r="I18" s="44" t="n"/>
+      <c r="J18" s="43" t="inlineStr">
         <is>
           <t>14b</t>
         </is>
       </c>
-      <c r="K18" s="43" t="n"/>
-      <c r="L18" s="43" t="n"/>
-      <c r="M18" s="43" t="n"/>
-      <c r="N18" s="43" t="n"/>
-      <c r="O18" s="43" t="n"/>
-      <c r="P18" s="43" t="n"/>
-      <c r="Q18" s="42" t="inlineStr">
+      <c r="K18" s="44" t="n"/>
+      <c r="L18" s="44" t="n"/>
+      <c r="M18" s="44" t="n"/>
+      <c r="N18" s="44" t="n"/>
+      <c r="O18" s="44" t="n"/>
+      <c r="P18" s="44" t="n"/>
+      <c r="Q18" s="43" t="inlineStr">
         <is>
           <t>19b</t>
         </is>
       </c>
-      <c r="R18" s="43" t="n"/>
-      <c r="S18" s="43" t="n"/>
-      <c r="T18" s="43" t="n"/>
-      <c r="U18" s="43" t="n"/>
-      <c r="V18" s="43" t="n"/>
-      <c r="W18" s="43" t="n"/>
-      <c r="X18" s="42" t="inlineStr">
+      <c r="R18" s="44" t="n"/>
+      <c r="S18" s="44" t="n"/>
+      <c r="T18" s="44" t="n"/>
+      <c r="U18" s="44" t="n"/>
+      <c r="V18" s="44" t="n"/>
+      <c r="W18" s="44" t="n"/>
+      <c r="X18" s="43" t="inlineStr">
         <is>
           <t>11b</t>
         </is>
       </c>
-      <c r="Y18" s="43" t="n"/>
-      <c r="Z18" s="43" t="n"/>
-      <c r="AA18" s="43" t="n"/>
-      <c r="AB18" s="43" t="n"/>
-      <c r="AC18" s="43" t="n"/>
-      <c r="AD18" s="43" t="n"/>
-      <c r="AE18" s="42" t="inlineStr">
+      <c r="Y18" s="44" t="n"/>
+      <c r="Z18" s="44" t="n"/>
+      <c r="AA18" s="44" t="n"/>
+      <c r="AB18" s="44" t="n"/>
+      <c r="AC18" s="44" t="n"/>
+      <c r="AD18" s="44" t="n"/>
+      <c r="AE18" s="43" t="inlineStr">
         <is>
           <t>10b</t>
         </is>
       </c>
-      <c r="AF18" s="43" t="n"/>
-      <c r="AG18" s="43" t="n"/>
-      <c r="AH18" s="43" t="n"/>
-      <c r="AI18" s="43" t="n"/>
-      <c r="AJ18" s="43" t="n"/>
-      <c r="AK18" s="43" t="n"/>
-      <c r="AL18" s="41" t="n"/>
-      <c r="AM18" s="41" t="n"/>
-      <c r="AN18" s="41" t="n"/>
-      <c r="AO18" s="41" t="n"/>
-      <c r="AP18" s="41" t="n"/>
-      <c r="AQ18" s="41" t="n"/>
-      <c r="AR18" s="41" t="n"/>
-      <c r="AS18" s="41" t="n"/>
-      <c r="AT18" s="41" t="n"/>
-      <c r="AU18" s="41" t="n"/>
-      <c r="AV18" s="41" t="n"/>
-      <c r="AW18" s="41" t="n"/>
-      <c r="AX18" s="41" t="n"/>
-      <c r="AY18" s="41" t="n"/>
-      <c r="AZ18" s="41" t="n"/>
-      <c r="BA18" s="41" t="n"/>
-      <c r="BB18" s="41" t="n"/>
-      <c r="BC18" s="41" t="n"/>
-      <c r="BD18" s="41" t="n"/>
-      <c r="BE18" s="41" t="n"/>
-      <c r="BF18" s="41" t="n"/>
-      <c r="BG18" s="41" t="n"/>
-      <c r="BH18" s="41" t="n"/>
-      <c r="BI18" s="41" t="n"/>
-      <c r="BJ18" s="41" t="n"/>
-      <c r="BK18" s="41" t="n"/>
-      <c r="BL18" s="41" t="n"/>
-      <c r="BM18" s="41" t="n"/>
-      <c r="BN18" s="41" t="n"/>
-      <c r="BO18" s="41" t="n"/>
-      <c r="BP18" s="41" t="n"/>
-      <c r="BQ18" s="41" t="n"/>
-      <c r="BR18" s="41" t="n"/>
-      <c r="BS18" s="41" t="n"/>
-      <c r="BT18" s="41" t="n"/>
-      <c r="BU18" s="41" t="n"/>
-      <c r="BV18" s="41" t="n"/>
-      <c r="BW18" s="41" t="n"/>
-      <c r="BX18" s="41" t="n"/>
-      <c r="BY18" s="41" t="n"/>
-      <c r="BZ18" s="41" t="n"/>
-      <c r="CA18" s="41" t="n"/>
-      <c r="CB18" s="41" t="n"/>
-      <c r="CC18" s="41" t="n"/>
-      <c r="CD18" s="41" t="n"/>
-      <c r="CE18" s="41" t="n"/>
-      <c r="CF18" s="41" t="n"/>
-      <c r="CG18" s="41" t="n"/>
-      <c r="CH18" s="41" t="n"/>
-      <c r="CI18" s="41" t="n"/>
-      <c r="CJ18" s="41" t="n"/>
-      <c r="CK18" s="41" t="n"/>
-      <c r="CL18" s="41" t="n"/>
-      <c r="CM18" s="41" t="n"/>
-      <c r="CN18" s="41" t="n"/>
-      <c r="CO18" s="41" t="n"/>
-      <c r="CP18" s="41" t="n"/>
-      <c r="CQ18" s="41" t="n"/>
-      <c r="CR18" s="41" t="n"/>
-      <c r="CS18" s="41" t="n"/>
-      <c r="CT18" s="41" t="n"/>
-      <c r="CU18" s="41" t="n"/>
-      <c r="CV18" s="41" t="n"/>
-      <c r="CW18" s="41" t="n"/>
-      <c r="CX18" s="41" t="n"/>
-      <c r="CY18" s="41" t="n"/>
-      <c r="CZ18" s="41" t="n"/>
+      <c r="AF18" s="44" t="n"/>
+      <c r="AG18" s="44" t="n"/>
+      <c r="AH18" s="44" t="n"/>
+      <c r="AI18" s="44" t="n"/>
+      <c r="AJ18" s="44" t="n"/>
+      <c r="AK18" s="44" t="n"/>
+      <c r="AL18" s="42" t="n"/>
+      <c r="AM18" s="42" t="n"/>
+      <c r="AN18" s="42" t="n"/>
+      <c r="AO18" s="42" t="n"/>
+      <c r="AP18" s="42" t="n"/>
+      <c r="AQ18" s="42" t="n"/>
+      <c r="AR18" s="42" t="n"/>
+      <c r="AS18" s="42" t="n"/>
+      <c r="AT18" s="42" t="n"/>
+      <c r="AU18" s="42" t="n"/>
+      <c r="AV18" s="42" t="n"/>
+      <c r="AW18" s="42" t="n"/>
+      <c r="AX18" s="42" t="n"/>
+      <c r="AY18" s="42" t="n"/>
+      <c r="AZ18" s="42" t="n"/>
+      <c r="BA18" s="42" t="n"/>
+      <c r="BB18" s="42" t="n"/>
+      <c r="BC18" s="42" t="n"/>
+      <c r="BD18" s="42" t="n"/>
+      <c r="BE18" s="42" t="n"/>
+      <c r="BF18" s="42" t="n"/>
+      <c r="BG18" s="42" t="n"/>
+      <c r="BH18" s="42" t="n"/>
+      <c r="BI18" s="42" t="n"/>
+      <c r="BJ18" s="42" t="n"/>
+      <c r="BK18" s="42" t="n"/>
+      <c r="BL18" s="42" t="n"/>
+      <c r="BM18" s="42" t="n"/>
+      <c r="BN18" s="42" t="n"/>
+      <c r="BO18" s="42" t="n"/>
+      <c r="BP18" s="42" t="n"/>
+      <c r="BQ18" s="42" t="n"/>
+      <c r="BR18" s="42" t="n"/>
+      <c r="BS18" s="42" t="n"/>
+      <c r="BT18" s="42" t="n"/>
+      <c r="BU18" s="42" t="n"/>
+      <c r="BV18" s="42" t="n"/>
+      <c r="BW18" s="42" t="n"/>
+      <c r="BX18" s="42" t="n"/>
+      <c r="BY18" s="42" t="n"/>
+      <c r="BZ18" s="42" t="n"/>
+      <c r="CA18" s="42" t="n"/>
+      <c r="CB18" s="42" t="n"/>
+      <c r="CC18" s="42" t="n"/>
+      <c r="CD18" s="42" t="n"/>
+      <c r="CE18" s="42" t="n"/>
+      <c r="CF18" s="42" t="n"/>
+      <c r="CG18" s="42" t="n"/>
+      <c r="CH18" s="42" t="n"/>
+      <c r="CI18" s="42" t="n"/>
+      <c r="CJ18" s="42" t="n"/>
+      <c r="CK18" s="42" t="n"/>
+      <c r="CL18" s="42" t="n"/>
+      <c r="CM18" s="42" t="n"/>
+      <c r="CN18" s="42" t="n"/>
+      <c r="CO18" s="42" t="n"/>
+      <c r="CP18" s="42" t="n"/>
+      <c r="CQ18" s="42" t="n"/>
+      <c r="CR18" s="42" t="n"/>
+      <c r="CS18" s="42" t="n"/>
+      <c r="CT18" s="42" t="n"/>
+      <c r="CU18" s="42" t="n"/>
+      <c r="CV18" s="42" t="n"/>
+      <c r="CW18" s="42" t="n"/>
+      <c r="CX18" s="42" t="n"/>
+      <c r="CY18" s="42" t="n"/>
+      <c r="CZ18" s="42" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="C19" s="44" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>Rec +</t>
         </is>
       </c>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="41" t="n"/>
-      <c r="G19" s="41" t="n"/>
-      <c r="H19" s="41" t="n"/>
-      <c r="I19" s="41" t="n"/>
-      <c r="J19" s="41" t="n"/>
-      <c r="K19" s="41" t="n"/>
-      <c r="L19" s="41" t="n"/>
-      <c r="M19" s="41" t="n"/>
-      <c r="N19" s="41" t="n"/>
-      <c r="O19" s="41" t="n"/>
-      <c r="P19" s="41" t="n"/>
-      <c r="Q19" s="41" t="n"/>
-      <c r="R19" s="41" t="n"/>
-      <c r="S19" s="41" t="n"/>
-      <c r="T19" s="41" t="n"/>
-      <c r="U19" s="41" t="n"/>
-      <c r="V19" s="41" t="n"/>
-      <c r="W19" s="41" t="n"/>
-      <c r="X19" s="41" t="n"/>
-      <c r="Y19" s="41" t="n"/>
-      <c r="Z19" s="41" t="n"/>
-      <c r="AA19" s="41" t="n"/>
-      <c r="AB19" s="41" t="n"/>
-      <c r="AC19" s="41" t="n"/>
-      <c r="AD19" s="41" t="n"/>
-      <c r="AE19" s="41" t="n"/>
-      <c r="AF19" s="41" t="n"/>
-      <c r="AG19" s="41" t="n"/>
-      <c r="AH19" s="41" t="n"/>
-      <c r="AI19" s="41" t="n"/>
-      <c r="AJ19" s="41" t="n"/>
-      <c r="AK19" s="41" t="n"/>
-      <c r="AL19" s="45" t="inlineStr">
+      <c r="D19" s="42" t="n"/>
+      <c r="E19" s="42" t="n"/>
+      <c r="F19" s="42" t="n"/>
+      <c r="G19" s="42" t="n"/>
+      <c r="H19" s="42" t="n"/>
+      <c r="I19" s="42" t="n"/>
+      <c r="J19" s="42" t="n"/>
+      <c r="K19" s="42" t="n"/>
+      <c r="L19" s="42" t="n"/>
+      <c r="M19" s="42" t="n"/>
+      <c r="N19" s="42" t="n"/>
+      <c r="O19" s="42" t="n"/>
+      <c r="P19" s="42" t="n"/>
+      <c r="Q19" s="42" t="n"/>
+      <c r="R19" s="42" t="n"/>
+      <c r="S19" s="42" t="n"/>
+      <c r="T19" s="42" t="n"/>
+      <c r="U19" s="42" t="n"/>
+      <c r="V19" s="42" t="n"/>
+      <c r="W19" s="42" t="n"/>
+      <c r="X19" s="42" t="n"/>
+      <c r="Y19" s="42" t="n"/>
+      <c r="Z19" s="42" t="n"/>
+      <c r="AA19" s="42" t="n"/>
+      <c r="AB19" s="42" t="n"/>
+      <c r="AC19" s="42" t="n"/>
+      <c r="AD19" s="42" t="n"/>
+      <c r="AE19" s="42" t="n"/>
+      <c r="AF19" s="42" t="n"/>
+      <c r="AG19" s="42" t="n"/>
+      <c r="AH19" s="42" t="n"/>
+      <c r="AI19" s="42" t="n"/>
+      <c r="AJ19" s="42" t="n"/>
+      <c r="AK19" s="42" t="n"/>
+      <c r="AL19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AM19" s="46" t="n"/>
-      <c r="AN19" s="46" t="n"/>
-      <c r="AO19" s="46" t="n"/>
-      <c r="AP19" s="46" t="n"/>
-      <c r="AQ19" s="41" t="n"/>
-      <c r="AR19" s="41" t="n"/>
-      <c r="AS19" s="45" t="inlineStr">
+      <c r="AM19" s="48" t="n"/>
+      <c r="AN19" s="48" t="n"/>
+      <c r="AO19" s="48" t="n"/>
+      <c r="AP19" s="48" t="n"/>
+      <c r="AQ19" s="42" t="n"/>
+      <c r="AR19" s="42" t="n"/>
+      <c r="AS19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AT19" s="46" t="n"/>
-      <c r="AU19" s="46" t="n"/>
-      <c r="AV19" s="46" t="n"/>
-      <c r="AW19" s="46" t="n"/>
-      <c r="AX19" s="41" t="n"/>
-      <c r="AY19" s="45" t="inlineStr">
+      <c r="AT19" s="48" t="n"/>
+      <c r="AU19" s="48" t="n"/>
+      <c r="AV19" s="48" t="n"/>
+      <c r="AW19" s="48" t="n"/>
+      <c r="AX19" s="42" t="n"/>
+      <c r="AY19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AZ19" s="46" t="n"/>
-      <c r="BA19" s="46" t="n"/>
-      <c r="BB19" s="46" t="n"/>
-      <c r="BC19" s="46" t="n"/>
-      <c r="BD19" s="46" t="n"/>
-      <c r="BE19" s="41" t="n"/>
-      <c r="BF19" s="45" t="inlineStr">
+      <c r="AZ19" s="48" t="n"/>
+      <c r="BA19" s="48" t="n"/>
+      <c r="BB19" s="48" t="n"/>
+      <c r="BC19" s="48" t="n"/>
+      <c r="BD19" s="48" t="n"/>
+      <c r="BE19" s="42" t="n"/>
+      <c r="BF19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BG19" s="46" t="n"/>
-      <c r="BH19" s="46" t="n"/>
-      <c r="BI19" s="46" t="n"/>
-      <c r="BJ19" s="46" t="n"/>
-      <c r="BK19" s="46" t="n"/>
-      <c r="BL19" s="41" t="n"/>
-      <c r="BM19" s="45" t="inlineStr">
+      <c r="BG19" s="48" t="n"/>
+      <c r="BH19" s="48" t="n"/>
+      <c r="BI19" s="48" t="n"/>
+      <c r="BJ19" s="48" t="n"/>
+      <c r="BK19" s="48" t="n"/>
+      <c r="BL19" s="42" t="n"/>
+      <c r="BM19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BN19" s="46" t="n"/>
-      <c r="BO19" s="46" t="n"/>
-      <c r="BP19" s="46" t="n"/>
-      <c r="BQ19" s="46" t="n"/>
-      <c r="BR19" s="46" t="n"/>
-      <c r="BS19" s="41" t="n"/>
-      <c r="BT19" s="45" t="inlineStr">
+      <c r="BN19" s="48" t="n"/>
+      <c r="BO19" s="48" t="n"/>
+      <c r="BP19" s="48" t="n"/>
+      <c r="BQ19" s="48" t="n"/>
+      <c r="BR19" s="48" t="n"/>
+      <c r="BS19" s="42" t="n"/>
+      <c r="BT19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BU19" s="46" t="n"/>
-      <c r="BV19" s="46" t="n"/>
-      <c r="BW19" s="46" t="n"/>
-      <c r="BX19" s="46" t="n"/>
-      <c r="BY19" s="41" t="n"/>
-      <c r="BZ19" s="41" t="n"/>
-      <c r="CA19" s="45" t="inlineStr">
+      <c r="BU19" s="48" t="n"/>
+      <c r="BV19" s="48" t="n"/>
+      <c r="BW19" s="48" t="n"/>
+      <c r="BX19" s="48" t="n"/>
+      <c r="BY19" s="42" t="n"/>
+      <c r="BZ19" s="42" t="n"/>
+      <c r="CA19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CB19" s="46" t="n"/>
-      <c r="CC19" s="46" t="n"/>
-      <c r="CD19" s="46" t="n"/>
-      <c r="CE19" s="46" t="n"/>
-      <c r="CF19" s="41" t="n"/>
-      <c r="CG19" s="41" t="n"/>
-      <c r="CH19" s="45" t="inlineStr">
+      <c r="CB19" s="48" t="n"/>
+      <c r="CC19" s="48" t="n"/>
+      <c r="CD19" s="48" t="n"/>
+      <c r="CE19" s="48" t="n"/>
+      <c r="CF19" s="42" t="n"/>
+      <c r="CG19" s="42" t="n"/>
+      <c r="CH19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CI19" s="46" t="n"/>
-      <c r="CJ19" s="46" t="n"/>
-      <c r="CK19" s="46" t="n"/>
-      <c r="CL19" s="46" t="n"/>
-      <c r="CM19" s="41" t="n"/>
-      <c r="CN19" s="45" t="inlineStr">
+      <c r="CI19" s="48" t="n"/>
+      <c r="CJ19" s="48" t="n"/>
+      <c r="CK19" s="48" t="n"/>
+      <c r="CL19" s="48" t="n"/>
+      <c r="CM19" s="42" t="n"/>
+      <c r="CN19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CO19" s="46" t="n"/>
-      <c r="CP19" s="46" t="n"/>
-      <c r="CQ19" s="46" t="n"/>
-      <c r="CR19" s="46" t="n"/>
-      <c r="CS19" s="46" t="n"/>
-      <c r="CT19" s="41" t="n"/>
-      <c r="CU19" s="45" t="inlineStr">
+      <c r="CO19" s="48" t="n"/>
+      <c r="CP19" s="48" t="n"/>
+      <c r="CQ19" s="48" t="n"/>
+      <c r="CR19" s="48" t="n"/>
+      <c r="CS19" s="48" t="n"/>
+      <c r="CT19" s="42" t="n"/>
+      <c r="CU19" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CV19" s="46" t="n"/>
-      <c r="CW19" s="46" t="n"/>
-      <c r="CX19" s="46" t="n"/>
-      <c r="CY19" s="46" t="n"/>
-      <c r="CZ19" s="41" t="n"/>
+      <c r="CV19" s="48" t="n"/>
+      <c r="CW19" s="48" t="n"/>
+      <c r="CX19" s="48" t="n"/>
+      <c r="CY19" s="48" t="n"/>
+      <c r="CZ19" s="42" t="n"/>
     </row>
     <row r="20" ht="4" customHeight="1"/>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>Cont. 7</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>95.0%</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>51.6%</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D21" s="37" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="E21" s="38" t="n"/>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="38" t="n"/>
-      <c r="H21" s="38" t="n"/>
-      <c r="I21" s="38" t="n"/>
-      <c r="J21" s="37" t="inlineStr">
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
+      <c r="H21" s="39" t="n"/>
+      <c r="I21" s="39" t="n"/>
+      <c r="J21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="K21" s="38" t="n"/>
-      <c r="L21" s="38" t="n"/>
-      <c r="M21" s="38" t="n"/>
-      <c r="N21" s="38" t="n"/>
-      <c r="O21" s="38" t="n"/>
-      <c r="P21" s="38" t="n"/>
-      <c r="Q21" s="37" t="inlineStr">
+      <c r="K21" s="39" t="n"/>
+      <c r="L21" s="39" t="n"/>
+      <c r="M21" s="39" t="n"/>
+      <c r="N21" s="39" t="n"/>
+      <c r="O21" s="39" t="n"/>
+      <c r="P21" s="39" t="n"/>
+      <c r="Q21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="R21" s="38" t="n"/>
-      <c r="S21" s="38" t="n"/>
-      <c r="T21" s="38" t="n"/>
-      <c r="U21" s="38" t="n"/>
-      <c r="V21" s="38" t="n"/>
-      <c r="W21" s="38" t="n"/>
-      <c r="X21" s="37" t="inlineStr">
+      <c r="R21" s="39" t="n"/>
+      <c r="S21" s="39" t="n"/>
+      <c r="T21" s="39" t="n"/>
+      <c r="U21" s="39" t="n"/>
+      <c r="V21" s="39" t="n"/>
+      <c r="W21" s="39" t="n"/>
+      <c r="X21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="Y21" s="38" t="n"/>
-      <c r="Z21" s="38" t="n"/>
-      <c r="AA21" s="38" t="n"/>
-      <c r="AB21" s="38" t="n"/>
-      <c r="AC21" s="38" t="n"/>
-      <c r="AD21" s="38" t="n"/>
-      <c r="AE21" s="37" t="inlineStr">
+      <c r="Y21" s="39" t="n"/>
+      <c r="Z21" s="39" t="n"/>
+      <c r="AA21" s="39" t="n"/>
+      <c r="AB21" s="39" t="n"/>
+      <c r="AC21" s="39" t="n"/>
+      <c r="AD21" s="39" t="n"/>
+      <c r="AE21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AF21" s="38" t="n"/>
-      <c r="AG21" s="38" t="n"/>
-      <c r="AH21" s="38" t="n"/>
-      <c r="AI21" s="38" t="n"/>
-      <c r="AJ21" s="38" t="n"/>
-      <c r="AK21" s="38" t="n"/>
-      <c r="AL21" s="37" t="inlineStr">
+      <c r="AF21" s="39" t="n"/>
+      <c r="AG21" s="39" t="n"/>
+      <c r="AH21" s="39" t="n"/>
+      <c r="AI21" s="39" t="n"/>
+      <c r="AJ21" s="39" t="n"/>
+      <c r="AK21" s="39" t="n"/>
+      <c r="AL21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AM21" s="38" t="n"/>
-      <c r="AN21" s="38" t="n"/>
-      <c r="AO21" s="38" t="n"/>
-      <c r="AP21" s="38" t="n"/>
-      <c r="AQ21" s="38" t="n"/>
-      <c r="AR21" s="38" t="n"/>
-      <c r="AS21" s="37" t="inlineStr">
+      <c r="AM21" s="39" t="n"/>
+      <c r="AN21" s="39" t="n"/>
+      <c r="AO21" s="39" t="n"/>
+      <c r="AP21" s="39" t="n"/>
+      <c r="AQ21" s="39" t="n"/>
+      <c r="AR21" s="39" t="n"/>
+      <c r="AS21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AT21" s="38" t="n"/>
-      <c r="AU21" s="38" t="n"/>
-      <c r="AV21" s="38" t="n"/>
-      <c r="AW21" s="38" t="n"/>
-      <c r="AX21" s="38" t="n"/>
-      <c r="AY21" s="37" t="inlineStr">
+      <c r="AT21" s="39" t="n"/>
+      <c r="AU21" s="39" t="n"/>
+      <c r="AV21" s="39" t="n"/>
+      <c r="AW21" s="39" t="n"/>
+      <c r="AX21" s="39" t="n"/>
+      <c r="AY21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AZ21" s="38" t="n"/>
-      <c r="BA21" s="38" t="n"/>
-      <c r="BB21" s="38" t="n"/>
-      <c r="BC21" s="38" t="n"/>
-      <c r="BD21" s="38" t="n"/>
-      <c r="BE21" s="38" t="n"/>
-      <c r="BF21" s="37" t="inlineStr">
+      <c r="AZ21" s="39" t="n"/>
+      <c r="BA21" s="39" t="n"/>
+      <c r="BB21" s="39" t="n"/>
+      <c r="BC21" s="39" t="n"/>
+      <c r="BD21" s="39" t="n"/>
+      <c r="BE21" s="39" t="n"/>
+      <c r="BF21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BG21" s="38" t="n"/>
-      <c r="BH21" s="38" t="n"/>
-      <c r="BI21" s="38" t="n"/>
-      <c r="BJ21" s="38" t="n"/>
-      <c r="BK21" s="38" t="n"/>
-      <c r="BL21" s="38" t="n"/>
-      <c r="BM21" s="37" t="inlineStr">
+      <c r="BG21" s="39" t="n"/>
+      <c r="BH21" s="39" t="n"/>
+      <c r="BI21" s="39" t="n"/>
+      <c r="BJ21" s="39" t="n"/>
+      <c r="BK21" s="39" t="n"/>
+      <c r="BL21" s="39" t="n"/>
+      <c r="BM21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BN21" s="38" t="n"/>
-      <c r="BO21" s="38" t="n"/>
-      <c r="BP21" s="38" t="n"/>
-      <c r="BQ21" s="38" t="n"/>
-      <c r="BR21" s="38" t="n"/>
-      <c r="BS21" s="38" t="n"/>
-      <c r="BT21" s="37" t="inlineStr">
+      <c r="BN21" s="39" t="n"/>
+      <c r="BO21" s="39" t="n"/>
+      <c r="BP21" s="39" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
+      <c r="BR21" s="39" t="n"/>
+      <c r="BS21" s="39" t="n"/>
+      <c r="BT21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BU21" s="38" t="n"/>
-      <c r="BV21" s="38" t="n"/>
-      <c r="BW21" s="38" t="n"/>
-      <c r="BX21" s="38" t="n"/>
-      <c r="BY21" s="38" t="n"/>
-      <c r="BZ21" s="38" t="n"/>
-      <c r="CA21" s="37" t="inlineStr">
+      <c r="BU21" s="39" t="n"/>
+      <c r="BV21" s="39" t="n"/>
+      <c r="BW21" s="39" t="n"/>
+      <c r="BX21" s="39" t="n"/>
+      <c r="BY21" s="39" t="n"/>
+      <c r="BZ21" s="39" t="n"/>
+      <c r="CA21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CB21" s="38" t="n"/>
-      <c r="CC21" s="38" t="n"/>
-      <c r="CD21" s="38" t="n"/>
-      <c r="CE21" s="38" t="n"/>
-      <c r="CF21" s="38" t="n"/>
-      <c r="CG21" s="38" t="n"/>
-      <c r="CH21" s="37" t="inlineStr">
+      <c r="CB21" s="39" t="n"/>
+      <c r="CC21" s="39" t="n"/>
+      <c r="CD21" s="39" t="n"/>
+      <c r="CE21" s="39" t="n"/>
+      <c r="CF21" s="39" t="n"/>
+      <c r="CG21" s="39" t="n"/>
+      <c r="CH21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CI21" s="38" t="n"/>
-      <c r="CJ21" s="38" t="n"/>
-      <c r="CK21" s="38" t="n"/>
-      <c r="CL21" s="38" t="n"/>
-      <c r="CM21" s="38" t="n"/>
-      <c r="CN21" s="37" t="inlineStr">
+      <c r="CI21" s="39" t="n"/>
+      <c r="CJ21" s="39" t="n"/>
+      <c r="CK21" s="39" t="n"/>
+      <c r="CL21" s="39" t="n"/>
+      <c r="CM21" s="39" t="n"/>
+      <c r="CN21" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CO21" s="38" t="n"/>
-      <c r="CP21" s="38" t="n"/>
-      <c r="CQ21" s="38" t="n"/>
-      <c r="CR21" s="38" t="n"/>
-      <c r="CS21" s="38" t="n"/>
-      <c r="CT21" s="38" t="n"/>
-      <c r="CU21" s="38" t="n"/>
-      <c r="CV21" s="41" t="n"/>
-      <c r="CW21" s="41" t="n"/>
-      <c r="CX21" s="41" t="n"/>
-      <c r="CY21" s="41" t="n"/>
-      <c r="CZ21" s="41" t="n"/>
+      <c r="CO21" s="39" t="n"/>
+      <c r="CP21" s="39" t="n"/>
+      <c r="CQ21" s="39" t="n"/>
+      <c r="CR21" s="39" t="n"/>
+      <c r="CS21" s="39" t="n"/>
+      <c r="CT21" s="39" t="n"/>
+      <c r="CU21" s="39" t="n"/>
+      <c r="CV21" s="42" t="n"/>
+      <c r="CW21" s="42" t="n"/>
+      <c r="CX21" s="42" t="n"/>
+      <c r="CY21" s="42" t="n"/>
+      <c r="CZ21" s="42" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="C22" s="44" t="inlineStr">
+      <c r="C22" s="46" t="inlineStr">
         <is>
           <t>Rec +</t>
         </is>
       </c>
-      <c r="D22" s="45" t="inlineStr">
+      <c r="D22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
-      <c r="H22" s="46" t="n"/>
-      <c r="I22" s="41" t="n"/>
-      <c r="J22" s="45" t="inlineStr">
+      <c r="E22" s="48" t="n"/>
+      <c r="F22" s="48" t="n"/>
+      <c r="G22" s="48" t="n"/>
+      <c r="H22" s="48" t="n"/>
+      <c r="I22" s="42" t="n"/>
+      <c r="J22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="K22" s="46" t="n"/>
-      <c r="L22" s="46" t="n"/>
-      <c r="M22" s="46" t="n"/>
-      <c r="N22" s="46" t="n"/>
-      <c r="O22" s="46" t="n"/>
-      <c r="P22" s="41" t="n"/>
-      <c r="Q22" s="45" t="inlineStr">
+      <c r="K22" s="48" t="n"/>
+      <c r="L22" s="48" t="n"/>
+      <c r="M22" s="48" t="n"/>
+      <c r="N22" s="48" t="n"/>
+      <c r="O22" s="48" t="n"/>
+      <c r="P22" s="42" t="n"/>
+      <c r="Q22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="R22" s="46" t="n"/>
-      <c r="S22" s="46" t="n"/>
-      <c r="T22" s="46" t="n"/>
-      <c r="U22" s="46" t="n"/>
-      <c r="V22" s="46" t="n"/>
-      <c r="W22" s="41" t="n"/>
-      <c r="X22" s="45" t="inlineStr">
+      <c r="R22" s="48" t="n"/>
+      <c r="S22" s="48" t="n"/>
+      <c r="T22" s="48" t="n"/>
+      <c r="U22" s="48" t="n"/>
+      <c r="V22" s="48" t="n"/>
+      <c r="W22" s="42" t="n"/>
+      <c r="X22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="Y22" s="46" t="n"/>
-      <c r="Z22" s="46" t="n"/>
-      <c r="AA22" s="46" t="n"/>
-      <c r="AB22" s="46" t="n"/>
-      <c r="AC22" s="46" t="n"/>
-      <c r="AD22" s="41" t="n"/>
-      <c r="AE22" s="45" t="inlineStr">
+      <c r="Y22" s="48" t="n"/>
+      <c r="Z22" s="48" t="n"/>
+      <c r="AA22" s="48" t="n"/>
+      <c r="AB22" s="48" t="n"/>
+      <c r="AC22" s="48" t="n"/>
+      <c r="AD22" s="42" t="n"/>
+      <c r="AE22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AF22" s="46" t="n"/>
-      <c r="AG22" s="46" t="n"/>
-      <c r="AH22" s="46" t="n"/>
-      <c r="AI22" s="46" t="n"/>
-      <c r="AJ22" s="41" t="n"/>
-      <c r="AK22" s="41" t="n"/>
-      <c r="AL22" s="45" t="inlineStr">
+      <c r="AF22" s="48" t="n"/>
+      <c r="AG22" s="48" t="n"/>
+      <c r="AH22" s="48" t="n"/>
+      <c r="AI22" s="48" t="n"/>
+      <c r="AJ22" s="42" t="n"/>
+      <c r="AK22" s="42" t="n"/>
+      <c r="AL22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AM22" s="46" t="n"/>
-      <c r="AN22" s="46" t="n"/>
-      <c r="AO22" s="46" t="n"/>
-      <c r="AP22" s="46" t="n"/>
-      <c r="AQ22" s="41" t="n"/>
-      <c r="AR22" s="41" t="n"/>
-      <c r="AS22" s="45" t="inlineStr">
+      <c r="AM22" s="48" t="n"/>
+      <c r="AN22" s="48" t="n"/>
+      <c r="AO22" s="48" t="n"/>
+      <c r="AP22" s="48" t="n"/>
+      <c r="AQ22" s="42" t="n"/>
+      <c r="AR22" s="42" t="n"/>
+      <c r="AS22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AT22" s="46" t="n"/>
-      <c r="AU22" s="46" t="n"/>
-      <c r="AV22" s="46" t="n"/>
-      <c r="AW22" s="46" t="n"/>
-      <c r="AX22" s="41" t="n"/>
-      <c r="AY22" s="45" t="inlineStr">
+      <c r="AT22" s="48" t="n"/>
+      <c r="AU22" s="48" t="n"/>
+      <c r="AV22" s="48" t="n"/>
+      <c r="AW22" s="48" t="n"/>
+      <c r="AX22" s="42" t="n"/>
+      <c r="AY22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AZ22" s="46" t="n"/>
-      <c r="BA22" s="46" t="n"/>
-      <c r="BB22" s="46" t="n"/>
-      <c r="BC22" s="46" t="n"/>
-      <c r="BD22" s="46" t="n"/>
-      <c r="BE22" s="41" t="n"/>
-      <c r="BF22" s="45" t="inlineStr">
+      <c r="AZ22" s="48" t="n"/>
+      <c r="BA22" s="48" t="n"/>
+      <c r="BB22" s="48" t="n"/>
+      <c r="BC22" s="48" t="n"/>
+      <c r="BD22" s="48" t="n"/>
+      <c r="BE22" s="42" t="n"/>
+      <c r="BF22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BG22" s="46" t="n"/>
-      <c r="BH22" s="46" t="n"/>
-      <c r="BI22" s="46" t="n"/>
-      <c r="BJ22" s="46" t="n"/>
-      <c r="BK22" s="46" t="n"/>
-      <c r="BL22" s="41" t="n"/>
-      <c r="BM22" s="45" t="inlineStr">
+      <c r="BG22" s="48" t="n"/>
+      <c r="BH22" s="48" t="n"/>
+      <c r="BI22" s="48" t="n"/>
+      <c r="BJ22" s="48" t="n"/>
+      <c r="BK22" s="48" t="n"/>
+      <c r="BL22" s="42" t="n"/>
+      <c r="BM22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BN22" s="46" t="n"/>
-      <c r="BO22" s="46" t="n"/>
-      <c r="BP22" s="46" t="n"/>
-      <c r="BQ22" s="46" t="n"/>
-      <c r="BR22" s="46" t="n"/>
-      <c r="BS22" s="41" t="n"/>
-      <c r="BT22" s="45" t="inlineStr">
+      <c r="BN22" s="48" t="n"/>
+      <c r="BO22" s="48" t="n"/>
+      <c r="BP22" s="48" t="n"/>
+      <c r="BQ22" s="48" t="n"/>
+      <c r="BR22" s="48" t="n"/>
+      <c r="BS22" s="42" t="n"/>
+      <c r="BT22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BU22" s="46" t="n"/>
-      <c r="BV22" s="46" t="n"/>
-      <c r="BW22" s="46" t="n"/>
-      <c r="BX22" s="46" t="n"/>
-      <c r="BY22" s="41" t="n"/>
-      <c r="BZ22" s="41" t="n"/>
-      <c r="CA22" s="45" t="inlineStr">
+      <c r="BU22" s="48" t="n"/>
+      <c r="BV22" s="48" t="n"/>
+      <c r="BW22" s="48" t="n"/>
+      <c r="BX22" s="48" t="n"/>
+      <c r="BY22" s="42" t="n"/>
+      <c r="BZ22" s="42" t="n"/>
+      <c r="CA22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CB22" s="46" t="n"/>
-      <c r="CC22" s="46" t="n"/>
-      <c r="CD22" s="46" t="n"/>
-      <c r="CE22" s="46" t="n"/>
-      <c r="CF22" s="41" t="n"/>
-      <c r="CG22" s="41" t="n"/>
-      <c r="CH22" s="45" t="inlineStr">
+      <c r="CB22" s="48" t="n"/>
+      <c r="CC22" s="48" t="n"/>
+      <c r="CD22" s="48" t="n"/>
+      <c r="CE22" s="48" t="n"/>
+      <c r="CF22" s="42" t="n"/>
+      <c r="CG22" s="42" t="n"/>
+      <c r="CH22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CI22" s="46" t="n"/>
-      <c r="CJ22" s="46" t="n"/>
-      <c r="CK22" s="46" t="n"/>
-      <c r="CL22" s="46" t="n"/>
-      <c r="CM22" s="41" t="n"/>
-      <c r="CN22" s="45" t="inlineStr">
+      <c r="CI22" s="48" t="n"/>
+      <c r="CJ22" s="48" t="n"/>
+      <c r="CK22" s="48" t="n"/>
+      <c r="CL22" s="48" t="n"/>
+      <c r="CM22" s="42" t="n"/>
+      <c r="CN22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CO22" s="46" t="n"/>
-      <c r="CP22" s="46" t="n"/>
-      <c r="CQ22" s="46" t="n"/>
-      <c r="CR22" s="46" t="n"/>
-      <c r="CS22" s="46" t="n"/>
-      <c r="CT22" s="41" t="n"/>
-      <c r="CU22" s="45" t="inlineStr">
+      <c r="CO22" s="48" t="n"/>
+      <c r="CP22" s="48" t="n"/>
+      <c r="CQ22" s="48" t="n"/>
+      <c r="CR22" s="48" t="n"/>
+      <c r="CS22" s="48" t="n"/>
+      <c r="CT22" s="42" t="n"/>
+      <c r="CU22" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CV22" s="46" t="n"/>
-      <c r="CW22" s="46" t="n"/>
-      <c r="CX22" s="46" t="n"/>
-      <c r="CY22" s="46" t="n"/>
-      <c r="CZ22" s="41" t="n"/>
+      <c r="CV22" s="48" t="n"/>
+      <c r="CW22" s="48" t="n"/>
+      <c r="CX22" s="48" t="n"/>
+      <c r="CY22" s="48" t="n"/>
+      <c r="CZ22" s="42" t="n"/>
     </row>
     <row r="23" ht="4" customHeight="1"/>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>Cont. 8</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>95.0%</t>
-        </is>
-      </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>51.6%</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D24" s="37" t="inlineStr">
+      <c r="D24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="E24" s="38" t="n"/>
-      <c r="F24" s="38" t="n"/>
-      <c r="G24" s="38" t="n"/>
-      <c r="H24" s="38" t="n"/>
-      <c r="I24" s="38" t="n"/>
-      <c r="J24" s="37" t="inlineStr">
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="K24" s="38" t="n"/>
-      <c r="L24" s="38" t="n"/>
-      <c r="M24" s="38" t="n"/>
-      <c r="N24" s="38" t="n"/>
-      <c r="O24" s="38" t="n"/>
-      <c r="P24" s="38" t="n"/>
-      <c r="Q24" s="37" t="inlineStr">
+      <c r="K24" s="39" t="n"/>
+      <c r="L24" s="39" t="n"/>
+      <c r="M24" s="39" t="n"/>
+      <c r="N24" s="39" t="n"/>
+      <c r="O24" s="39" t="n"/>
+      <c r="P24" s="39" t="n"/>
+      <c r="Q24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="R24" s="38" t="n"/>
-      <c r="S24" s="38" t="n"/>
-      <c r="T24" s="38" t="n"/>
-      <c r="U24" s="38" t="n"/>
-      <c r="V24" s="38" t="n"/>
-      <c r="W24" s="38" t="n"/>
-      <c r="X24" s="37" t="inlineStr">
+      <c r="R24" s="39" t="n"/>
+      <c r="S24" s="39" t="n"/>
+      <c r="T24" s="39" t="n"/>
+      <c r="U24" s="39" t="n"/>
+      <c r="V24" s="39" t="n"/>
+      <c r="W24" s="39" t="n"/>
+      <c r="X24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="Y24" s="38" t="n"/>
-      <c r="Z24" s="38" t="n"/>
-      <c r="AA24" s="38" t="n"/>
-      <c r="AB24" s="38" t="n"/>
-      <c r="AC24" s="38" t="n"/>
-      <c r="AD24" s="38" t="n"/>
-      <c r="AE24" s="37" t="inlineStr">
+      <c r="Y24" s="39" t="n"/>
+      <c r="Z24" s="39" t="n"/>
+      <c r="AA24" s="39" t="n"/>
+      <c r="AB24" s="39" t="n"/>
+      <c r="AC24" s="39" t="n"/>
+      <c r="AD24" s="39" t="n"/>
+      <c r="AE24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AF24" s="38" t="n"/>
-      <c r="AG24" s="38" t="n"/>
-      <c r="AH24" s="38" t="n"/>
-      <c r="AI24" s="38" t="n"/>
-      <c r="AJ24" s="38" t="n"/>
-      <c r="AK24" s="38" t="n"/>
-      <c r="AL24" s="37" t="inlineStr">
+      <c r="AF24" s="39" t="n"/>
+      <c r="AG24" s="39" t="n"/>
+      <c r="AH24" s="39" t="n"/>
+      <c r="AI24" s="39" t="n"/>
+      <c r="AJ24" s="39" t="n"/>
+      <c r="AK24" s="39" t="n"/>
+      <c r="AL24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AM24" s="38" t="n"/>
-      <c r="AN24" s="38" t="n"/>
-      <c r="AO24" s="38" t="n"/>
-      <c r="AP24" s="38" t="n"/>
-      <c r="AQ24" s="38" t="n"/>
-      <c r="AR24" s="38" t="n"/>
-      <c r="AS24" s="37" t="inlineStr">
+      <c r="AM24" s="39" t="n"/>
+      <c r="AN24" s="39" t="n"/>
+      <c r="AO24" s="39" t="n"/>
+      <c r="AP24" s="39" t="n"/>
+      <c r="AQ24" s="39" t="n"/>
+      <c r="AR24" s="39" t="n"/>
+      <c r="AS24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AT24" s="38" t="n"/>
-      <c r="AU24" s="38" t="n"/>
-      <c r="AV24" s="38" t="n"/>
-      <c r="AW24" s="38" t="n"/>
-      <c r="AX24" s="38" t="n"/>
-      <c r="AY24" s="37" t="inlineStr">
+      <c r="AT24" s="39" t="n"/>
+      <c r="AU24" s="39" t="n"/>
+      <c r="AV24" s="39" t="n"/>
+      <c r="AW24" s="39" t="n"/>
+      <c r="AX24" s="39" t="n"/>
+      <c r="AY24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="AZ24" s="38" t="n"/>
-      <c r="BA24" s="38" t="n"/>
-      <c r="BB24" s="38" t="n"/>
-      <c r="BC24" s="38" t="n"/>
-      <c r="BD24" s="38" t="n"/>
-      <c r="BE24" s="38" t="n"/>
-      <c r="BF24" s="37" t="inlineStr">
+      <c r="AZ24" s="39" t="n"/>
+      <c r="BA24" s="39" t="n"/>
+      <c r="BB24" s="39" t="n"/>
+      <c r="BC24" s="39" t="n"/>
+      <c r="BD24" s="39" t="n"/>
+      <c r="BE24" s="39" t="n"/>
+      <c r="BF24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BG24" s="38" t="n"/>
-      <c r="BH24" s="38" t="n"/>
-      <c r="BI24" s="38" t="n"/>
-      <c r="BJ24" s="38" t="n"/>
-      <c r="BK24" s="38" t="n"/>
-      <c r="BL24" s="38" t="n"/>
-      <c r="BM24" s="37" t="inlineStr">
+      <c r="BG24" s="39" t="n"/>
+      <c r="BH24" s="39" t="n"/>
+      <c r="BI24" s="39" t="n"/>
+      <c r="BJ24" s="39" t="n"/>
+      <c r="BK24" s="39" t="n"/>
+      <c r="BL24" s="39" t="n"/>
+      <c r="BM24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BN24" s="38" t="n"/>
-      <c r="BO24" s="38" t="n"/>
-      <c r="BP24" s="38" t="n"/>
-      <c r="BQ24" s="38" t="n"/>
-      <c r="BR24" s="38" t="n"/>
-      <c r="BS24" s="38" t="n"/>
-      <c r="BT24" s="37" t="inlineStr">
+      <c r="BN24" s="39" t="n"/>
+      <c r="BO24" s="39" t="n"/>
+      <c r="BP24" s="39" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
+      <c r="BR24" s="39" t="n"/>
+      <c r="BS24" s="39" t="n"/>
+      <c r="BT24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="BU24" s="38" t="n"/>
-      <c r="BV24" s="38" t="n"/>
-      <c r="BW24" s="38" t="n"/>
-      <c r="BX24" s="38" t="n"/>
-      <c r="BY24" s="38" t="n"/>
-      <c r="BZ24" s="38" t="n"/>
-      <c r="CA24" s="37" t="inlineStr">
+      <c r="BU24" s="39" t="n"/>
+      <c r="BV24" s="39" t="n"/>
+      <c r="BW24" s="39" t="n"/>
+      <c r="BX24" s="39" t="n"/>
+      <c r="BY24" s="39" t="n"/>
+      <c r="BZ24" s="39" t="n"/>
+      <c r="CA24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CB24" s="38" t="n"/>
-      <c r="CC24" s="38" t="n"/>
-      <c r="CD24" s="38" t="n"/>
-      <c r="CE24" s="38" t="n"/>
-      <c r="CF24" s="38" t="n"/>
-      <c r="CG24" s="38" t="n"/>
-      <c r="CH24" s="37" t="inlineStr">
+      <c r="CB24" s="39" t="n"/>
+      <c r="CC24" s="39" t="n"/>
+      <c r="CD24" s="39" t="n"/>
+      <c r="CE24" s="39" t="n"/>
+      <c r="CF24" s="39" t="n"/>
+      <c r="CG24" s="39" t="n"/>
+      <c r="CH24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CI24" s="38" t="n"/>
-      <c r="CJ24" s="38" t="n"/>
-      <c r="CK24" s="38" t="n"/>
-      <c r="CL24" s="38" t="n"/>
-      <c r="CM24" s="38" t="n"/>
-      <c r="CN24" s="37" t="inlineStr">
+      <c r="CI24" s="39" t="n"/>
+      <c r="CJ24" s="39" t="n"/>
+      <c r="CK24" s="39" t="n"/>
+      <c r="CL24" s="39" t="n"/>
+      <c r="CM24" s="39" t="n"/>
+      <c r="CN24" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="CO24" s="38" t="n"/>
-      <c r="CP24" s="38" t="n"/>
-      <c r="CQ24" s="38" t="n"/>
-      <c r="CR24" s="38" t="n"/>
-      <c r="CS24" s="38" t="n"/>
-      <c r="CT24" s="38" t="n"/>
-      <c r="CU24" s="38" t="n"/>
-      <c r="CV24" s="41" t="n"/>
-      <c r="CW24" s="41" t="n"/>
-      <c r="CX24" s="41" t="n"/>
-      <c r="CY24" s="41" t="n"/>
-      <c r="CZ24" s="41" t="n"/>
+      <c r="CO24" s="39" t="n"/>
+      <c r="CP24" s="39" t="n"/>
+      <c r="CQ24" s="39" t="n"/>
+      <c r="CR24" s="39" t="n"/>
+      <c r="CS24" s="39" t="n"/>
+      <c r="CT24" s="39" t="n"/>
+      <c r="CU24" s="39" t="n"/>
+      <c r="CV24" s="42" t="n"/>
+      <c r="CW24" s="42" t="n"/>
+      <c r="CX24" s="42" t="n"/>
+      <c r="CY24" s="42" t="n"/>
+      <c r="CZ24" s="42" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="C25" s="44" t="inlineStr">
+      <c r="C25" s="46" t="inlineStr">
         <is>
           <t>Rec +</t>
         </is>
       </c>
-      <c r="D25" s="45" t="inlineStr">
+      <c r="D25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="46" t="n"/>
-      <c r="G25" s="46" t="n"/>
-      <c r="H25" s="46" t="n"/>
-      <c r="I25" s="41" t="n"/>
-      <c r="J25" s="45" t="inlineStr">
+      <c r="E25" s="48" t="n"/>
+      <c r="F25" s="48" t="n"/>
+      <c r="G25" s="48" t="n"/>
+      <c r="H25" s="48" t="n"/>
+      <c r="I25" s="42" t="n"/>
+      <c r="J25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="K25" s="46" t="n"/>
-      <c r="L25" s="46" t="n"/>
-      <c r="M25" s="46" t="n"/>
-      <c r="N25" s="46" t="n"/>
-      <c r="O25" s="46" t="n"/>
-      <c r="P25" s="41" t="n"/>
-      <c r="Q25" s="45" t="inlineStr">
+      <c r="K25" s="48" t="n"/>
+      <c r="L25" s="48" t="n"/>
+      <c r="M25" s="48" t="n"/>
+      <c r="N25" s="48" t="n"/>
+      <c r="O25" s="48" t="n"/>
+      <c r="P25" s="42" t="n"/>
+      <c r="Q25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="R25" s="46" t="n"/>
-      <c r="S25" s="46" t="n"/>
-      <c r="T25" s="46" t="n"/>
-      <c r="U25" s="46" t="n"/>
-      <c r="V25" s="46" t="n"/>
-      <c r="W25" s="41" t="n"/>
-      <c r="X25" s="45" t="inlineStr">
+      <c r="R25" s="48" t="n"/>
+      <c r="S25" s="48" t="n"/>
+      <c r="T25" s="48" t="n"/>
+      <c r="U25" s="48" t="n"/>
+      <c r="V25" s="48" t="n"/>
+      <c r="W25" s="42" t="n"/>
+      <c r="X25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="Y25" s="46" t="n"/>
-      <c r="Z25" s="46" t="n"/>
-      <c r="AA25" s="46" t="n"/>
-      <c r="AB25" s="46" t="n"/>
-      <c r="AC25" s="46" t="n"/>
-      <c r="AD25" s="41" t="n"/>
-      <c r="AE25" s="45" t="inlineStr">
+      <c r="Y25" s="48" t="n"/>
+      <c r="Z25" s="48" t="n"/>
+      <c r="AA25" s="48" t="n"/>
+      <c r="AB25" s="48" t="n"/>
+      <c r="AC25" s="48" t="n"/>
+      <c r="AD25" s="42" t="n"/>
+      <c r="AE25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AF25" s="46" t="n"/>
-      <c r="AG25" s="46" t="n"/>
-      <c r="AH25" s="46" t="n"/>
-      <c r="AI25" s="46" t="n"/>
-      <c r="AJ25" s="41" t="n"/>
-      <c r="AK25" s="41" t="n"/>
-      <c r="AL25" s="45" t="inlineStr">
+      <c r="AF25" s="48" t="n"/>
+      <c r="AG25" s="48" t="n"/>
+      <c r="AH25" s="48" t="n"/>
+      <c r="AI25" s="48" t="n"/>
+      <c r="AJ25" s="42" t="n"/>
+      <c r="AK25" s="42" t="n"/>
+      <c r="AL25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AM25" s="46" t="n"/>
-      <c r="AN25" s="46" t="n"/>
-      <c r="AO25" s="46" t="n"/>
-      <c r="AP25" s="46" t="n"/>
-      <c r="AQ25" s="41" t="n"/>
-      <c r="AR25" s="41" t="n"/>
-      <c r="AS25" s="45" t="inlineStr">
+      <c r="AM25" s="48" t="n"/>
+      <c r="AN25" s="48" t="n"/>
+      <c r="AO25" s="48" t="n"/>
+      <c r="AP25" s="48" t="n"/>
+      <c r="AQ25" s="42" t="n"/>
+      <c r="AR25" s="42" t="n"/>
+      <c r="AS25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AT25" s="46" t="n"/>
-      <c r="AU25" s="46" t="n"/>
-      <c r="AV25" s="46" t="n"/>
-      <c r="AW25" s="46" t="n"/>
-      <c r="AX25" s="41" t="n"/>
-      <c r="AY25" s="45" t="inlineStr">
+      <c r="AT25" s="48" t="n"/>
+      <c r="AU25" s="48" t="n"/>
+      <c r="AV25" s="48" t="n"/>
+      <c r="AW25" s="48" t="n"/>
+      <c r="AX25" s="42" t="n"/>
+      <c r="AY25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AZ25" s="46" t="n"/>
-      <c r="BA25" s="46" t="n"/>
-      <c r="BB25" s="46" t="n"/>
-      <c r="BC25" s="46" t="n"/>
-      <c r="BD25" s="46" t="n"/>
-      <c r="BE25" s="41" t="n"/>
-      <c r="BF25" s="45" t="inlineStr">
+      <c r="AZ25" s="48" t="n"/>
+      <c r="BA25" s="48" t="n"/>
+      <c r="BB25" s="48" t="n"/>
+      <c r="BC25" s="48" t="n"/>
+      <c r="BD25" s="48" t="n"/>
+      <c r="BE25" s="42" t="n"/>
+      <c r="BF25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BG25" s="46" t="n"/>
-      <c r="BH25" s="46" t="n"/>
-      <c r="BI25" s="46" t="n"/>
-      <c r="BJ25" s="46" t="n"/>
-      <c r="BK25" s="46" t="n"/>
-      <c r="BL25" s="41" t="n"/>
-      <c r="BM25" s="45" t="inlineStr">
+      <c r="BG25" s="48" t="n"/>
+      <c r="BH25" s="48" t="n"/>
+      <c r="BI25" s="48" t="n"/>
+      <c r="BJ25" s="48" t="n"/>
+      <c r="BK25" s="48" t="n"/>
+      <c r="BL25" s="42" t="n"/>
+      <c r="BM25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BN25" s="46" t="n"/>
-      <c r="BO25" s="46" t="n"/>
-      <c r="BP25" s="46" t="n"/>
-      <c r="BQ25" s="46" t="n"/>
-      <c r="BR25" s="46" t="n"/>
-      <c r="BS25" s="41" t="n"/>
-      <c r="BT25" s="45" t="inlineStr">
+      <c r="BN25" s="48" t="n"/>
+      <c r="BO25" s="48" t="n"/>
+      <c r="BP25" s="48" t="n"/>
+      <c r="BQ25" s="48" t="n"/>
+      <c r="BR25" s="48" t="n"/>
+      <c r="BS25" s="42" t="n"/>
+      <c r="BT25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BU25" s="46" t="n"/>
-      <c r="BV25" s="46" t="n"/>
-      <c r="BW25" s="46" t="n"/>
-      <c r="BX25" s="46" t="n"/>
-      <c r="BY25" s="41" t="n"/>
-      <c r="BZ25" s="41" t="n"/>
-      <c r="CA25" s="45" t="inlineStr">
+      <c r="BU25" s="48" t="n"/>
+      <c r="BV25" s="48" t="n"/>
+      <c r="BW25" s="48" t="n"/>
+      <c r="BX25" s="48" t="n"/>
+      <c r="BY25" s="42" t="n"/>
+      <c r="BZ25" s="42" t="n"/>
+      <c r="CA25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CB25" s="46" t="n"/>
-      <c r="CC25" s="46" t="n"/>
-      <c r="CD25" s="46" t="n"/>
-      <c r="CE25" s="46" t="n"/>
-      <c r="CF25" s="41" t="n"/>
-      <c r="CG25" s="41" t="n"/>
-      <c r="CH25" s="45" t="inlineStr">
+      <c r="CB25" s="48" t="n"/>
+      <c r="CC25" s="48" t="n"/>
+      <c r="CD25" s="48" t="n"/>
+      <c r="CE25" s="48" t="n"/>
+      <c r="CF25" s="42" t="n"/>
+      <c r="CG25" s="42" t="n"/>
+      <c r="CH25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CI25" s="46" t="n"/>
-      <c r="CJ25" s="46" t="n"/>
-      <c r="CK25" s="46" t="n"/>
-      <c r="CL25" s="46" t="n"/>
-      <c r="CM25" s="41" t="n"/>
-      <c r="CN25" s="45" t="inlineStr">
+      <c r="CI25" s="48" t="n"/>
+      <c r="CJ25" s="48" t="n"/>
+      <c r="CK25" s="48" t="n"/>
+      <c r="CL25" s="48" t="n"/>
+      <c r="CM25" s="42" t="n"/>
+      <c r="CN25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CO25" s="46" t="n"/>
-      <c r="CP25" s="46" t="n"/>
-      <c r="CQ25" s="46" t="n"/>
-      <c r="CR25" s="46" t="n"/>
-      <c r="CS25" s="46" t="n"/>
-      <c r="CT25" s="41" t="n"/>
-      <c r="CU25" s="45" t="inlineStr">
+      <c r="CO25" s="48" t="n"/>
+      <c r="CP25" s="48" t="n"/>
+      <c r="CQ25" s="48" t="n"/>
+      <c r="CR25" s="48" t="n"/>
+      <c r="CS25" s="48" t="n"/>
+      <c r="CT25" s="42" t="n"/>
+      <c r="CU25" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CV25" s="46" t="n"/>
-      <c r="CW25" s="46" t="n"/>
-      <c r="CX25" s="46" t="n"/>
-      <c r="CY25" s="46" t="n"/>
-      <c r="CZ25" s="41" t="n"/>
+      <c r="CV25" s="48" t="n"/>
+      <c r="CW25" s="48" t="n"/>
+      <c r="CX25" s="48" t="n"/>
+      <c r="CY25" s="48" t="n"/>
+      <c r="CZ25" s="42" t="n"/>
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>Cont. 9</t>
         </is>
       </c>
-      <c r="B27" s="47" t="inlineStr">
-        <is>
-          <t>13.2%</t>
-        </is>
-      </c>
-      <c r="C27" s="36" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>Pallets</t>
         </is>
       </c>
-      <c r="D27" s="37" t="inlineStr">
+      <c r="D27" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="E27" s="38" t="n"/>
-      <c r="F27" s="38" t="n"/>
-      <c r="G27" s="38" t="n"/>
-      <c r="H27" s="38" t="n"/>
-      <c r="I27" s="38" t="n"/>
-      <c r="J27" s="37" t="inlineStr">
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
+      <c r="H27" s="39" t="n"/>
+      <c r="I27" s="39" t="n"/>
+      <c r="J27" s="38" t="inlineStr">
         <is>
           <t>115x77(2p)</t>
         </is>
       </c>
-      <c r="K27" s="38" t="n"/>
-      <c r="L27" s="38" t="n"/>
-      <c r="M27" s="38" t="n"/>
-      <c r="N27" s="38" t="n"/>
-      <c r="O27" s="38" t="n"/>
-      <c r="P27" s="38" t="n"/>
-      <c r="Q27" s="38" t="n"/>
-      <c r="R27" s="41" t="n"/>
-      <c r="S27" s="41" t="n"/>
-      <c r="T27" s="41" t="n"/>
-      <c r="U27" s="41" t="n"/>
-      <c r="V27" s="41" t="n"/>
-      <c r="W27" s="41" t="n"/>
-      <c r="X27" s="41" t="n"/>
-      <c r="Y27" s="41" t="n"/>
-      <c r="Z27" s="41" t="n"/>
-      <c r="AA27" s="41" t="n"/>
-      <c r="AB27" s="41" t="n"/>
-      <c r="AC27" s="41" t="n"/>
-      <c r="AD27" s="41" t="n"/>
-      <c r="AE27" s="41" t="n"/>
-      <c r="AF27" s="41" t="n"/>
-      <c r="AG27" s="41" t="n"/>
-      <c r="AH27" s="41" t="n"/>
-      <c r="AI27" s="41" t="n"/>
-      <c r="AJ27" s="41" t="n"/>
-      <c r="AK27" s="41" t="n"/>
-      <c r="AL27" s="41" t="n"/>
-      <c r="AM27" s="41" t="n"/>
-      <c r="AN27" s="41" t="n"/>
-      <c r="AO27" s="41" t="n"/>
-      <c r="AP27" s="41" t="n"/>
-      <c r="AQ27" s="41" t="n"/>
-      <c r="AR27" s="41" t="n"/>
-      <c r="AS27" s="41" t="n"/>
-      <c r="AT27" s="41" t="n"/>
-      <c r="AU27" s="41" t="n"/>
-      <c r="AV27" s="41" t="n"/>
-      <c r="AW27" s="41" t="n"/>
-      <c r="AX27" s="41" t="n"/>
-      <c r="AY27" s="41" t="n"/>
-      <c r="AZ27" s="41" t="n"/>
-      <c r="BA27" s="41" t="n"/>
-      <c r="BB27" s="41" t="n"/>
-      <c r="BC27" s="41" t="n"/>
-      <c r="BD27" s="41" t="n"/>
-      <c r="BE27" s="41" t="n"/>
-      <c r="BF27" s="41" t="n"/>
-      <c r="BG27" s="41" t="n"/>
-      <c r="BH27" s="41" t="n"/>
-      <c r="BI27" s="41" t="n"/>
-      <c r="BJ27" s="41" t="n"/>
-      <c r="BK27" s="41" t="n"/>
-      <c r="BL27" s="41" t="n"/>
-      <c r="BM27" s="41" t="n"/>
-      <c r="BN27" s="41" t="n"/>
-      <c r="BO27" s="41" t="n"/>
-      <c r="BP27" s="41" t="n"/>
-      <c r="BQ27" s="41" t="n"/>
-      <c r="BR27" s="41" t="n"/>
-      <c r="BS27" s="41" t="n"/>
-      <c r="BT27" s="41" t="n"/>
-      <c r="BU27" s="41" t="n"/>
-      <c r="BV27" s="41" t="n"/>
-      <c r="BW27" s="41" t="n"/>
-      <c r="BX27" s="41" t="n"/>
-      <c r="BY27" s="41" t="n"/>
-      <c r="BZ27" s="41" t="n"/>
-      <c r="CA27" s="41" t="n"/>
-      <c r="CB27" s="41" t="n"/>
-      <c r="CC27" s="41" t="n"/>
-      <c r="CD27" s="41" t="n"/>
-      <c r="CE27" s="41" t="n"/>
-      <c r="CF27" s="41" t="n"/>
-      <c r="CG27" s="41" t="n"/>
-      <c r="CH27" s="41" t="n"/>
-      <c r="CI27" s="41" t="n"/>
-      <c r="CJ27" s="41" t="n"/>
-      <c r="CK27" s="41" t="n"/>
-      <c r="CL27" s="41" t="n"/>
-      <c r="CM27" s="41" t="n"/>
-      <c r="CN27" s="41" t="n"/>
-      <c r="CO27" s="41" t="n"/>
-      <c r="CP27" s="41" t="n"/>
-      <c r="CQ27" s="41" t="n"/>
-      <c r="CR27" s="41" t="n"/>
-      <c r="CS27" s="41" t="n"/>
-      <c r="CT27" s="41" t="n"/>
-      <c r="CU27" s="41" t="n"/>
-      <c r="CV27" s="41" t="n"/>
-      <c r="CW27" s="41" t="n"/>
-      <c r="CX27" s="41" t="n"/>
-      <c r="CY27" s="41" t="n"/>
-      <c r="CZ27" s="41" t="n"/>
+      <c r="K27" s="39" t="n"/>
+      <c r="L27" s="39" t="n"/>
+      <c r="M27" s="39" t="n"/>
+      <c r="N27" s="39" t="n"/>
+      <c r="O27" s="39" t="n"/>
+      <c r="P27" s="39" t="n"/>
+      <c r="Q27" s="39" t="n"/>
+      <c r="R27" s="42" t="n"/>
+      <c r="S27" s="42" t="n"/>
+      <c r="T27" s="42" t="n"/>
+      <c r="U27" s="42" t="n"/>
+      <c r="V27" s="42" t="n"/>
+      <c r="W27" s="42" t="n"/>
+      <c r="X27" s="42" t="n"/>
+      <c r="Y27" s="42" t="n"/>
+      <c r="Z27" s="42" t="n"/>
+      <c r="AA27" s="42" t="n"/>
+      <c r="AB27" s="42" t="n"/>
+      <c r="AC27" s="42" t="n"/>
+      <c r="AD27" s="42" t="n"/>
+      <c r="AE27" s="42" t="n"/>
+      <c r="AF27" s="42" t="n"/>
+      <c r="AG27" s="42" t="n"/>
+      <c r="AH27" s="42" t="n"/>
+      <c r="AI27" s="42" t="n"/>
+      <c r="AJ27" s="42" t="n"/>
+      <c r="AK27" s="42" t="n"/>
+      <c r="AL27" s="42" t="n"/>
+      <c r="AM27" s="42" t="n"/>
+      <c r="AN27" s="42" t="n"/>
+      <c r="AO27" s="42" t="n"/>
+      <c r="AP27" s="42" t="n"/>
+      <c r="AQ27" s="42" t="n"/>
+      <c r="AR27" s="42" t="n"/>
+      <c r="AS27" s="42" t="n"/>
+      <c r="AT27" s="42" t="n"/>
+      <c r="AU27" s="42" t="n"/>
+      <c r="AV27" s="42" t="n"/>
+      <c r="AW27" s="42" t="n"/>
+      <c r="AX27" s="42" t="n"/>
+      <c r="AY27" s="42" t="n"/>
+      <c r="AZ27" s="42" t="n"/>
+      <c r="BA27" s="42" t="n"/>
+      <c r="BB27" s="42" t="n"/>
+      <c r="BC27" s="42" t="n"/>
+      <c r="BD27" s="42" t="n"/>
+      <c r="BE27" s="42" t="n"/>
+      <c r="BF27" s="42" t="n"/>
+      <c r="BG27" s="42" t="n"/>
+      <c r="BH27" s="42" t="n"/>
+      <c r="BI27" s="42" t="n"/>
+      <c r="BJ27" s="42" t="n"/>
+      <c r="BK27" s="42" t="n"/>
+      <c r="BL27" s="42" t="n"/>
+      <c r="BM27" s="42" t="n"/>
+      <c r="BN27" s="42" t="n"/>
+      <c r="BO27" s="42" t="n"/>
+      <c r="BP27" s="42" t="n"/>
+      <c r="BQ27" s="42" t="n"/>
+      <c r="BR27" s="42" t="n"/>
+      <c r="BS27" s="42" t="n"/>
+      <c r="BT27" s="42" t="n"/>
+      <c r="BU27" s="42" t="n"/>
+      <c r="BV27" s="42" t="n"/>
+      <c r="BW27" s="42" t="n"/>
+      <c r="BX27" s="42" t="n"/>
+      <c r="BY27" s="42" t="n"/>
+      <c r="BZ27" s="42" t="n"/>
+      <c r="CA27" s="42" t="n"/>
+      <c r="CB27" s="42" t="n"/>
+      <c r="CC27" s="42" t="n"/>
+      <c r="CD27" s="42" t="n"/>
+      <c r="CE27" s="42" t="n"/>
+      <c r="CF27" s="42" t="n"/>
+      <c r="CG27" s="42" t="n"/>
+      <c r="CH27" s="42" t="n"/>
+      <c r="CI27" s="42" t="n"/>
+      <c r="CJ27" s="42" t="n"/>
+      <c r="CK27" s="42" t="n"/>
+      <c r="CL27" s="42" t="n"/>
+      <c r="CM27" s="42" t="n"/>
+      <c r="CN27" s="42" t="n"/>
+      <c r="CO27" s="42" t="n"/>
+      <c r="CP27" s="42" t="n"/>
+      <c r="CQ27" s="42" t="n"/>
+      <c r="CR27" s="42" t="n"/>
+      <c r="CS27" s="42" t="n"/>
+      <c r="CT27" s="42" t="n"/>
+      <c r="CU27" s="42" t="n"/>
+      <c r="CV27" s="42" t="n"/>
+      <c r="CW27" s="42" t="n"/>
+      <c r="CX27" s="42" t="n"/>
+      <c r="CY27" s="42" t="n"/>
+      <c r="CZ27" s="42" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="C28" s="44" t="inlineStr">
+      <c r="C28" s="46" t="inlineStr">
         <is>
           <t>Rec +</t>
         </is>
       </c>
-      <c r="D28" s="45" t="inlineStr">
+      <c r="D28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="46" t="n"/>
-      <c r="G28" s="46" t="n"/>
-      <c r="H28" s="46" t="n"/>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="45" t="inlineStr">
+      <c r="E28" s="48" t="n"/>
+      <c r="F28" s="48" t="n"/>
+      <c r="G28" s="48" t="n"/>
+      <c r="H28" s="48" t="n"/>
+      <c r="I28" s="42" t="n"/>
+      <c r="J28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="K28" s="46" t="n"/>
-      <c r="L28" s="46" t="n"/>
-      <c r="M28" s="46" t="n"/>
-      <c r="N28" s="46" t="n"/>
-      <c r="O28" s="46" t="n"/>
-      <c r="P28" s="41" t="n"/>
-      <c r="Q28" s="45" t="inlineStr">
+      <c r="K28" s="48" t="n"/>
+      <c r="L28" s="48" t="n"/>
+      <c r="M28" s="48" t="n"/>
+      <c r="N28" s="48" t="n"/>
+      <c r="O28" s="48" t="n"/>
+      <c r="P28" s="42" t="n"/>
+      <c r="Q28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="R28" s="46" t="n"/>
-      <c r="S28" s="46" t="n"/>
-      <c r="T28" s="46" t="n"/>
-      <c r="U28" s="46" t="n"/>
-      <c r="V28" s="45" t="inlineStr">
+      <c r="R28" s="48" t="n"/>
+      <c r="S28" s="48" t="n"/>
+      <c r="T28" s="48" t="n"/>
+      <c r="U28" s="48" t="n"/>
+      <c r="V28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="W28" s="46" t="n"/>
-      <c r="X28" s="46" t="n"/>
-      <c r="Y28" s="46" t="n"/>
-      <c r="Z28" s="46" t="n"/>
-      <c r="AA28" s="45" t="inlineStr">
+      <c r="W28" s="48" t="n"/>
+      <c r="X28" s="48" t="n"/>
+      <c r="Y28" s="48" t="n"/>
+      <c r="Z28" s="48" t="n"/>
+      <c r="AA28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AB28" s="46" t="n"/>
-      <c r="AC28" s="46" t="n"/>
-      <c r="AD28" s="46" t="n"/>
-      <c r="AE28" s="46" t="n"/>
-      <c r="AF28" s="45" t="inlineStr">
+      <c r="AB28" s="48" t="n"/>
+      <c r="AC28" s="48" t="n"/>
+      <c r="AD28" s="48" t="n"/>
+      <c r="AE28" s="48" t="n"/>
+      <c r="AF28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AG28" s="46" t="n"/>
-      <c r="AH28" s="46" t="n"/>
-      <c r="AI28" s="46" t="n"/>
-      <c r="AJ28" s="46" t="n"/>
-      <c r="AK28" s="45" t="inlineStr">
+      <c r="AG28" s="48" t="n"/>
+      <c r="AH28" s="48" t="n"/>
+      <c r="AI28" s="48" t="n"/>
+      <c r="AJ28" s="48" t="n"/>
+      <c r="AK28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AL28" s="46" t="n"/>
-      <c r="AM28" s="46" t="n"/>
-      <c r="AN28" s="46" t="n"/>
-      <c r="AO28" s="46" t="n"/>
-      <c r="AP28" s="45" t="inlineStr">
+      <c r="AL28" s="48" t="n"/>
+      <c r="AM28" s="48" t="n"/>
+      <c r="AN28" s="48" t="n"/>
+      <c r="AO28" s="48" t="n"/>
+      <c r="AP28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AQ28" s="46" t="n"/>
-      <c r="AR28" s="46" t="n"/>
-      <c r="AS28" s="46" t="n"/>
-      <c r="AT28" s="46" t="n"/>
-      <c r="AU28" s="45" t="inlineStr">
+      <c r="AQ28" s="48" t="n"/>
+      <c r="AR28" s="48" t="n"/>
+      <c r="AS28" s="48" t="n"/>
+      <c r="AT28" s="48" t="n"/>
+      <c r="AU28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="AV28" s="46" t="n"/>
-      <c r="AW28" s="46" t="n"/>
-      <c r="AX28" s="46" t="n"/>
-      <c r="AY28" s="46" t="n"/>
-      <c r="AZ28" s="45" t="inlineStr">
+      <c r="AV28" s="48" t="n"/>
+      <c r="AW28" s="48" t="n"/>
+      <c r="AX28" s="48" t="n"/>
+      <c r="AY28" s="48" t="n"/>
+      <c r="AZ28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BA28" s="46" t="n"/>
-      <c r="BB28" s="46" t="n"/>
-      <c r="BC28" s="46" t="n"/>
-      <c r="BD28" s="46" t="n"/>
-      <c r="BE28" s="45" t="inlineStr">
+      <c r="BA28" s="48" t="n"/>
+      <c r="BB28" s="48" t="n"/>
+      <c r="BC28" s="48" t="n"/>
+      <c r="BD28" s="48" t="n"/>
+      <c r="BE28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BF28" s="46" t="n"/>
-      <c r="BG28" s="46" t="n"/>
-      <c r="BH28" s="46" t="n"/>
-      <c r="BI28" s="46" t="n"/>
-      <c r="BJ28" s="46" t="n"/>
-      <c r="BK28" s="45" t="inlineStr">
+      <c r="BF28" s="48" t="n"/>
+      <c r="BG28" s="48" t="n"/>
+      <c r="BH28" s="48" t="n"/>
+      <c r="BI28" s="48" t="n"/>
+      <c r="BJ28" s="48" t="n"/>
+      <c r="BK28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BL28" s="46" t="n"/>
-      <c r="BM28" s="46" t="n"/>
-      <c r="BN28" s="46" t="n"/>
-      <c r="BO28" s="45" t="inlineStr">
+      <c r="BL28" s="48" t="n"/>
+      <c r="BM28" s="48" t="n"/>
+      <c r="BN28" s="48" t="n"/>
+      <c r="BO28" s="47" t="inlineStr">
         <is>
           <t>+2p</t>
         </is>
       </c>
-      <c r="BP28" s="45" t="inlineStr">
+      <c r="BP28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BQ28" s="46" t="n"/>
-      <c r="BR28" s="46" t="n"/>
-      <c r="BS28" s="46" t="n"/>
-      <c r="BT28" s="46" t="n"/>
-      <c r="BU28" s="45" t="inlineStr">
+      <c r="BQ28" s="48" t="n"/>
+      <c r="BR28" s="48" t="n"/>
+      <c r="BS28" s="48" t="n"/>
+      <c r="BT28" s="48" t="n"/>
+      <c r="BU28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="BV28" s="46" t="n"/>
-      <c r="BW28" s="46" t="n"/>
-      <c r="BX28" s="46" t="n"/>
-      <c r="BY28" s="45" t="inlineStr">
+      <c r="BV28" s="48" t="n"/>
+      <c r="BW28" s="48" t="n"/>
+      <c r="BX28" s="48" t="n"/>
+      <c r="BY28" s="47" t="inlineStr">
         <is>
           <t>+2p</t>
         </is>
       </c>
-      <c r="BZ28" s="45" t="inlineStr">
+      <c r="BZ28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CA28" s="46" t="n"/>
-      <c r="CB28" s="46" t="n"/>
-      <c r="CC28" s="46" t="n"/>
-      <c r="CD28" s="46" t="n"/>
-      <c r="CE28" s="45" t="inlineStr">
+      <c r="CA28" s="48" t="n"/>
+      <c r="CB28" s="48" t="n"/>
+      <c r="CC28" s="48" t="n"/>
+      <c r="CD28" s="48" t="n"/>
+      <c r="CE28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CF28" s="46" t="n"/>
-      <c r="CG28" s="46" t="n"/>
-      <c r="CH28" s="46" t="n"/>
-      <c r="CI28" s="45" t="inlineStr">
+      <c r="CF28" s="48" t="n"/>
+      <c r="CG28" s="48" t="n"/>
+      <c r="CH28" s="48" t="n"/>
+      <c r="CI28" s="47" t="inlineStr">
         <is>
           <t>+2p</t>
         </is>
       </c>
-      <c r="CJ28" s="45" t="inlineStr">
+      <c r="CJ28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CK28" s="46" t="n"/>
-      <c r="CL28" s="46" t="n"/>
-      <c r="CM28" s="46" t="n"/>
-      <c r="CN28" s="46" t="n"/>
-      <c r="CO28" s="45" t="inlineStr">
+      <c r="CK28" s="48" t="n"/>
+      <c r="CL28" s="48" t="n"/>
+      <c r="CM28" s="48" t="n"/>
+      <c r="CN28" s="48" t="n"/>
+      <c r="CO28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CP28" s="46" t="n"/>
-      <c r="CQ28" s="46" t="n"/>
-      <c r="CR28" s="46" t="n"/>
-      <c r="CS28" s="45" t="inlineStr">
+      <c r="CP28" s="48" t="n"/>
+      <c r="CQ28" s="48" t="n"/>
+      <c r="CR28" s="48" t="n"/>
+      <c r="CS28" s="47" t="inlineStr">
         <is>
           <t>+2p</t>
         </is>
       </c>
-      <c r="CT28" s="45" t="inlineStr">
+      <c r="CT28" s="47" t="inlineStr">
         <is>
           <t>+4b</t>
         </is>
       </c>
-      <c r="CU28" s="46" t="n"/>
-      <c r="CV28" s="46" t="n"/>
-      <c r="CW28" s="46" t="n"/>
-      <c r="CX28" s="46" t="n"/>
-      <c r="CY28" s="46" t="n"/>
-      <c r="CZ28" s="48" t="n"/>
+      <c r="CU28" s="48" t="n"/>
+      <c r="CV28" s="48" t="n"/>
+      <c r="CW28" s="48" t="n"/>
+      <c r="CX28" s="48" t="n"/>
+      <c r="CY28" s="48" t="n"/>
+      <c r="CZ28" s="50" t="n"/>
     </row>
     <row r="29" ht="4" customHeight="1"/>
   </sheetData>
@@ -7772,28 +7783,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  FILL RECOMMENDATIONS — additional items to order to fill free container space</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  ✅ Tail Zone = unused length after last pallet block     ✅ Atop Zone = headroom above existing pallet rows</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 1   —   Tail: 2 cm → 2 cm  (0.0% filled)   |   +0 pallets  +0 NP boxes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">    No additions possible — no items from current order fit remaining free zones</t>
         </is>
@@ -7801,14 +7812,14 @@
     </row>
     <row r="6" ht="8" customHeight="1"/>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 2   —   Tail: 8 cm → 8 cm  (0.0% filled)   |   +0 pallets  +0 NP boxes</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">    No additions possible — no items from current order fit remaining free zones</t>
         </is>
@@ -7816,14 +7827,14 @@
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 3   —   Tail: 8 cm → 8 cm  (0.0% filled)   |   +0 pallets  +0 NP boxes</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">    No additions possible — no items from current order fit remaining free zones</t>
         </is>
@@ -7831,14 +7842,14 @@
     </row>
     <row r="12" ht="8" customHeight="1"/>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 4   —   Tail: 8 cm → 8 cm  (0.0% filled)   |   +0 pallets  +0 NP boxes</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">    No additions possible — no items from current order fit remaining free zones</t>
         </is>
@@ -7846,14 +7857,14 @@
     </row>
     <row r="15" ht="8" customHeight="1"/>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 5   —   Tail: 8 cm → 8 cm  (0.0% filled)   |   +0 pallets  +0 NP boxes</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="50" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">    No additions possible — no items from current order fit remaining free zones</t>
         </is>
@@ -7861,7 +7872,7 @@
     </row>
     <row r="18" ht="8" customHeight="1"/>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 6   —   Tail: 60 cm → 9 cm  (85.0% filled)   |   +0 pallets  +49 NP boxes</t>
         </is>
@@ -7915,17 +7926,17 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="51" t="inlineStr">
+      <c r="A21" s="53" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B21" s="52" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>NP box  (5× across width)</t>
         </is>
       </c>
-      <c r="C21" s="53" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h40xd45cm | [8720362378730]  [46×46×87cm]</t>
         </is>
@@ -7952,17 +7963,17 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="A22" s="53" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B22" s="54" t="inlineStr">
+      <c r="B22" s="56" t="inlineStr">
         <is>
           <t>NP box  (4× across width)</t>
         </is>
       </c>
-      <c r="C22" s="53" t="inlineStr">
+      <c r="C22" s="55" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]  [56×56×66cm]</t>
         </is>
@@ -7989,17 +8000,17 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="53" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B23" s="52" t="inlineStr">
+      <c r="B23" s="54" t="inlineStr">
         <is>
           <t>NP box  (4× across width)</t>
         </is>
       </c>
-      <c r="C23" s="53" t="inlineStr">
+      <c r="C23" s="55" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]  [56×56×66cm]</t>
         </is>
@@ -8026,15 +8037,15 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">   Total additions for Container 6</t>
         </is>
       </c>
-      <c r="H24" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="56" t="inlineStr">
+      <c r="H24" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="58" t="inlineStr">
         <is>
           <t>+49 boxes</t>
         </is>
@@ -8042,7 +8053,7 @@
     </row>
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 7   —   Tail: 60 cm → 9 cm  (85.0% filled)   |   +0 pallets  +69 NP boxes</t>
         </is>
@@ -8096,17 +8107,17 @@
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="51" t="inlineStr">
+      <c r="A28" s="53" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B28" s="52" t="inlineStr">
+      <c r="B28" s="54" t="inlineStr">
         <is>
           <t>NP box  (5× across width)</t>
         </is>
       </c>
-      <c r="C28" s="53" t="inlineStr">
+      <c r="C28" s="55" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h40xd45cm | [8720362378730]  [46×46×87cm]</t>
         </is>
@@ -8133,17 +8144,17 @@
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="51" t="inlineStr">
+      <c r="A29" s="53" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B29" s="54" t="inlineStr">
+      <c r="B29" s="56" t="inlineStr">
         <is>
           <t>NP box  (4× across width)</t>
         </is>
       </c>
-      <c r="C29" s="53" t="inlineStr">
+      <c r="C29" s="55" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]  [56×56×66cm]</t>
         </is>
@@ -8170,17 +8181,17 @@
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="51" t="inlineStr">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B30" s="52" t="inlineStr">
+      <c r="B30" s="54" t="inlineStr">
         <is>
           <t>NP box  (4× across width)</t>
         </is>
       </c>
-      <c r="C30" s="53" t="inlineStr">
+      <c r="C30" s="55" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]  [56×56×66cm]</t>
         </is>
@@ -8207,15 +8218,15 @@
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="55" t="inlineStr">
+      <c r="A31" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">   Total additions for Container 7</t>
         </is>
       </c>
-      <c r="H31" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="56" t="inlineStr">
+      <c r="H31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="58" t="inlineStr">
         <is>
           <t>+69 boxes</t>
         </is>
@@ -8223,7 +8234,7 @@
     </row>
     <row r="32" ht="8" customHeight="1"/>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 8   —   Tail: 60 cm → 9 cm  (85.0% filled)   |   +0 pallets  +69 NP boxes</t>
         </is>
@@ -8277,17 +8288,17 @@
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="51" t="inlineStr">
+      <c r="A35" s="53" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B35" s="52" t="inlineStr">
+      <c r="B35" s="54" t="inlineStr">
         <is>
           <t>NP box  (5× across width)</t>
         </is>
       </c>
-      <c r="C35" s="53" t="inlineStr">
+      <c r="C35" s="55" t="inlineStr">
         <is>
           <t>Bravo pot round l. grey zinc finish - h40xd45cm | [8720362378730]  [46×46×87cm]</t>
         </is>
@@ -8314,17 +8325,17 @@
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="51" t="inlineStr">
+      <c r="A36" s="53" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B36" s="54" t="inlineStr">
+      <c r="B36" s="56" t="inlineStr">
         <is>
           <t>NP box  (4× across width)</t>
         </is>
       </c>
-      <c r="C36" s="53" t="inlineStr">
+      <c r="C36" s="55" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]  [56×56×66cm]</t>
         </is>
@@ -8351,17 +8362,17 @@
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="51" t="inlineStr">
+      <c r="A37" s="53" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B37" s="52" t="inlineStr">
+      <c r="B37" s="54" t="inlineStr">
         <is>
           <t>NP box  (4× across width)</t>
         </is>
       </c>
-      <c r="C37" s="53" t="inlineStr">
+      <c r="C37" s="55" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]  [56×56×66cm]</t>
         </is>
@@ -8388,15 +8399,15 @@
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="55" t="inlineStr">
+      <c r="A38" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">   Total additions for Container 8</t>
         </is>
       </c>
-      <c r="H38" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="56" t="inlineStr">
+      <c r="H38" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="58" t="inlineStr">
         <is>
           <t>+69 boxes</t>
         </is>
@@ -8404,7 +8415,7 @@
     </row>
     <row r="39" ht="8" customHeight="1"/>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Container 9   —   Tail: 1044 cm → 2 cm  (99.8% filled)   |   +18 pallets  +76 NP boxes</t>
         </is>
@@ -8458,17 +8469,17 @@
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="57" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B42" s="52" t="inlineStr">
+      <c r="B42" s="54" t="inlineStr">
         <is>
           <t>Pallet block</t>
         </is>
       </c>
-      <c r="C42" s="58" t="inlineStr">
+      <c r="C42" s="60" t="inlineStr">
         <is>
           <t>115x77|&gt;130  —  2 pallets/block</t>
         </is>
@@ -8495,17 +8506,17 @@
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="57" t="inlineStr">
+      <c r="A43" s="59" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B43" s="54" t="inlineStr">
+      <c r="B43" s="56" t="inlineStr">
         <is>
           <t>Pallet block</t>
         </is>
       </c>
-      <c r="C43" s="58" t="inlineStr">
+      <c r="C43" s="60" t="inlineStr">
         <is>
           <t>115x77|&gt;130  —  2 pallets/block</t>
         </is>
@@ -8532,17 +8543,17 @@
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="51" t="inlineStr">
+      <c r="A44" s="53" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B44" s="52" t="inlineStr">
+      <c r="B44" s="54" t="inlineStr">
         <is>
           <t>NP box  (4× across width)</t>
         </is>
       </c>
-      <c r="C44" s="53" t="inlineStr">
+      <c r="C44" s="55" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]  [56×56×66cm]</t>
         </is>
@@ -8569,17 +8580,17 @@
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="51" t="inlineStr">
+      <c r="A45" s="53" t="inlineStr">
         <is>
           <t>ATOP</t>
         </is>
       </c>
-      <c r="B45" s="52" t="inlineStr">
+      <c r="B45" s="54" t="inlineStr">
         <is>
           <t>NP box  (4× across width)</t>
         </is>
       </c>
-      <c r="C45" s="53" t="inlineStr">
+      <c r="C45" s="55" t="inlineStr">
         <is>
           <t>Bravo bowl round l. grey zinc finish - h26xd55cm | [8718861700367]  [56×56×66cm]</t>
         </is>
@@ -8606,15 +8617,15 @@
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="55" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">   Total additions for Container 9</t>
         </is>
       </c>
-      <c r="H46" s="56" t="n">
+      <c r="H46" s="58" t="n">
         <v>18</v>
       </c>
-      <c r="I46" s="56" t="inlineStr">
+      <c r="I46" s="58" t="inlineStr">
         <is>
           <t>+76 boxes</t>
         </is>
